--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -548,8 +548,60 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-10-01 06:40:23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026/10/01 06:40:23</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-09-30 23:43:02</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J2"/>
+  <autoFilter ref="A1:J3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -612,7 +664,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
         <v>673.51</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -600,8 +600,60 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-10-01 09:55:05</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026/10/01 09:55:05</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-10-01 02:28:31</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J3"/>
+  <autoFilter ref="A1:J4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -664,7 +716,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
         <v>673.51</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -652,8 +652,60 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:16:13</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026/10/01 17:16:13</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-10-01 09:20:43</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J4"/>
+  <autoFilter ref="A1:J5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -716,7 +768,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
         <v>673.51</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -704,8 +704,60 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:05</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026/10/02 00:00:05</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:34:08</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J5"/>
+  <autoFilter ref="A1:J6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -716,7 +768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -780,61 +832,102 @@
         <v>673.51</v>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>673.51</v>
+      </c>
+      <c r="D5" t="n">
+        <v>673.51</v>
+      </c>
+      <c r="E5" t="n">
+        <v>673.51</v>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>firstPublishTime</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>middle</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>publishTimeRaw</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>2026-10-01 02:49:02</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>673.51</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>2026/10/01 02:49:02</t>
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:05</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026/10/02 00:00:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E4"/>
+  <autoFilter ref="A1:E5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -756,8 +756,60 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-10-02 06:47:48</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026/10/02 06:47:48</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:55:06</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J6"/>
+  <autoFilter ref="A1:J7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -839,7 +891,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
         <v>673.51</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -808,8 +808,60 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-10-02 14:41:18</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026/10/02 14:41:18</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-10-02 06:45:56</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J7"/>
+  <autoFilter ref="A1:J8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -891,7 +943,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
         <v>673.51</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -860,8 +860,60 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-10-02 21:13:33</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026/10/02 21:13:33</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-10-02 13:14:33</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J8"/>
+  <autoFilter ref="A1:J9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -943,7 +995,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
         <v>673.51</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -912,8 +912,60 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-10-03 00:00:05</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026/10/03 00:00:05</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-10-02 18:30:11</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J9"/>
+  <autoFilter ref="A1:J10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -924,7 +976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1007,83 +1059,124 @@
         <v>673.51</v>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>673.51</v>
+      </c>
+      <c r="D6" t="n">
+        <v>673.51</v>
+      </c>
+      <c r="E6" t="n">
+        <v>673.51</v>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-01 02:49:02</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>673.51</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/10/01 02:49:02</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-10-01 02:49:02</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026/10/01 02:49:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>2026-10-02 00:00:05</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>673.51</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>2026/10/02 00:00:05</t>
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-10-03 00:00:05</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026/10/03 00:00:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E5"/>
+  <autoFilter ref="A1:E6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -964,8 +964,60 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-10-03 05:30:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026/10/03 05:30:00</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-10-02 22:29:55</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J10"/>
+  <autoFilter ref="A1:J11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1066,7 +1118,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
         <v>673.51</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1016,8 +1016,60 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-10-03 10:30:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026/10/03 10:30:00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-10-03 06:44:25</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J11"/>
+  <autoFilter ref="A1:J12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1118,7 +1170,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
         <v>673.51</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1068,8 +1068,60 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-10-04 00:00:05</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026/10/04 00:00:05</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-10-03 16:11:55</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J12"/>
+  <autoFilter ref="A1:J13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1080,7 +1132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1182,68 +1234,65 @@
         <v>673.51</v>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>673.51</v>
+      </c>
+      <c r="D7" t="n">
+        <v>673.51</v>
+      </c>
+      <c r="E7" t="n">
+        <v>673.51</v>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-01 02:49:02</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>673.51</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026/10/01 02:49:02</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:05</t>
+          <t>2026-10-01 02:49:02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1253,34 +1302,78 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/10/02 00:00:05</t>
+          <t>2026/10/01 02:49:02</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-10-02 00:00:05</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026/10/02 00:00:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>2026-10-03 00:00:05</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>673.51</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>2026/10/03 00:00:05</t>
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-10-04 00:00:05</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026/10/04 00:00:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E6"/>
+  <autoFilter ref="A1:E7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1120,8 +1120,60 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-10-04 05:30:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026/10/04 05:30:00</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-10-03 22:11:04</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J13"/>
+  <autoFilter ref="A1:J14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1241,7 +1293,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
         <v>673.51</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1172,8 +1172,60 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-10-04 10:30:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026/10/04 10:30:00</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-10-04 06:22:10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J14"/>
+  <autoFilter ref="A1:J15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1293,7 +1345,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
         <v>673.51</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1224,8 +1224,60 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-10-05 00:00:05</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026/10/05 00:00:05</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-10-04 17:02:35</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J15"/>
+  <autoFilter ref="A1:J16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1236,7 +1288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1357,68 +1409,65 @@
         <v>673.51</v>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>673.51</v>
+      </c>
+      <c r="D8" t="n">
+        <v>673.51</v>
+      </c>
+      <c r="E8" t="n">
+        <v>673.51</v>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-01 02:49:02</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>673.51</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/10/01 02:49:02</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:05</t>
+          <t>2026-10-01 02:49:02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1428,19 +1477,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/10/02 00:00:05</t>
+          <t>2026/10/01 02:49:02</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03 00:00:05</t>
+          <t>2026-10-02 00:00:05</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1450,34 +1499,78 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026/10/03 00:00:05</t>
+          <t>2026/10/02 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-10-03 00:00:05</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026/10/03 00:00:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>2026-10-04 00:00:05</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>673.51</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>2026/10/04 00:00:05</t>
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-10-05 00:00:05</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026/10/05 00:00:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E7"/>
+  <autoFilter ref="A1:E8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1276,8 +1276,60 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-10-05 05:30:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>669.87</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>672.69</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026/10/05 05:30:00</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-10-04 23:04:34</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J16"/>
+  <autoFilter ref="A1:J17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1416,7 +1468,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
         <v>673.51</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1328,8 +1328,60 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-10-05 08:50:45</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>669.63</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>669.63</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>672.44</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>672.44</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026/10/05 08:50:45</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:55:13</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J17"/>
+  <autoFilter ref="A1:J18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1468,7 +1520,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
         <v>673.51</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1380,8 +1380,60 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:27:15</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>669.73</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>669.73</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>672.54</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>672.54</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026/10/05 16:27:15</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-10-05 08:31:15</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J18"/>
+  <autoFilter ref="A1:J19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1520,7 +1572,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
         <v>673.51</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1432,8 +1432,60 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-10-06 00:00:05</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>669.63</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>669.63</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>672.44</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>672.44</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026/10/06 00:00:05</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-10-05 17:21:39</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J19"/>
+  <autoFilter ref="A1:J20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1444,7 +1496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1584,68 +1636,65 @@
         <v>673.51</v>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>673.51</v>
+      </c>
+      <c r="D9" t="n">
+        <v>673.51</v>
+      </c>
+      <c r="E9" t="n">
+        <v>673.51</v>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-01 02:49:02</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>673.51</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/10/01 02:49:02</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:05</t>
+          <t>2026-10-01 02:49:02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1655,19 +1704,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026/10/02 00:00:05</t>
+          <t>2026/10/01 02:49:02</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-03 00:00:05</t>
+          <t>2026-10-02 00:00:05</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1677,19 +1726,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/10/03 00:00:05</t>
+          <t>2026/10/02 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-04 00:00:05</t>
+          <t>2026-10-03 00:00:05</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1699,34 +1748,78 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/10/04 00:00:05</t>
+          <t>2026/10/03 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-10-04 00:00:05</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026/10/04 00:00:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2026-10-05 00:00:05</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>673.51</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>2026/10/05 00:00:05</t>
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-10-06 00:00:05</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026/10/06 00:00:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E8"/>
+  <autoFilter ref="A1:E9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1484,8 +1484,60 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:40:24</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>669.63</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>669.63</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>672.44</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>672.44</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026/10/06 06:40:24</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-10-05 23:14:10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J20"/>
+  <autoFilter ref="A1:J21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1643,7 +1695,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
         <v>673.51</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1536,8 +1536,60 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:01:40</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>669.18</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>669.18</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>671.99</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>671.99</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026/10/06 11:01:40</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-10-06 03:04:58</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J21"/>
+  <autoFilter ref="A1:J22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1695,7 +1747,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
         <v>673.51</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1588,8 +1588,60 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-10-06 18:06:42</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>669.18</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>669.18</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>671.99</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>671.99</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026/10/06 18:06:42</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-10-06 10:10:07</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J22"/>
+  <autoFilter ref="A1:J23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1747,7 +1799,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
         <v>673.51</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1640,8 +1640,60 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:00:05</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>669.18</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>669.18</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>671.99</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>671.99</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026/10/07 00:00:05</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:49:10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J23"/>
+  <autoFilter ref="A1:J24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1652,7 +1704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1811,68 +1863,65 @@
         <v>673.51</v>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>673.51</v>
+      </c>
+      <c r="D10" t="n">
+        <v>673.51</v>
+      </c>
+      <c r="E10" t="n">
+        <v>673.51</v>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-01 02:49:02</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>673.51</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026/10/01 02:49:02</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:05</t>
+          <t>2026-10-01 02:49:02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1882,19 +1931,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/10/02 00:00:05</t>
+          <t>2026/10/01 02:49:02</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-03 00:00:05</t>
+          <t>2026-10-02 00:00:05</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1904,19 +1953,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/10/03 00:00:05</t>
+          <t>2026/10/02 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-04 00:00:05</t>
+          <t>2026-10-03 00:00:05</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1926,19 +1975,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/10/04 00:00:05</t>
+          <t>2026/10/03 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-05 00:00:05</t>
+          <t>2026-10-04 00:00:05</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1948,34 +1997,78 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026/10/05 00:00:05</t>
+          <t>2026/10/04 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-10-05 00:00:05</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026/10/05 00:00:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>2026-10-06 00:00:05</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>673.51</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>2026/10/06 00:00:05</t>
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:00:05</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026/10/07 00:00:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E9"/>
+  <autoFilter ref="A1:E10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1692,8 +1692,60 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-10-07 08:46:46</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>669.18</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>669.18</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>671.99</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>671.99</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026/10/07 08:46:46</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:49:50</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J24"/>
+  <autoFilter ref="A1:J25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1870,7 +1922,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
         <v>673.51</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1744,8 +1744,60 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:33:56</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>669.33</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>669.33</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>672.14</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>672.14</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026/10/07 14:33:56</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:37:35</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J25"/>
+  <autoFilter ref="A1:J26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1922,7 +1974,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
         <v>673.51</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1796,8 +1796,60 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-10-07 21:51:49</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>669.33</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>669.33</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>672.14</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>672.14</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026/10/07 21:51:49</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:55:41</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J26"/>
+  <autoFilter ref="A1:J27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1974,7 +2026,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
         <v>673.51</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1848,8 +1848,60 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-10-08 00:00:05</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>669.33</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>669.33</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>672.14</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>672.14</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026/10/08 00:00:05</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-10-07 19:47:17</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J27"/>
+  <autoFilter ref="A1:J28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1860,7 +1912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2038,68 +2090,65 @@
         <v>673.51</v>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>673.51</v>
+      </c>
+      <c r="D11" t="n">
+        <v>673.51</v>
+      </c>
+      <c r="E11" t="n">
+        <v>673.51</v>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-01 02:49:02</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>673.51</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/10/01 02:49:02</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:05</t>
+          <t>2026-10-01 02:49:02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2109,19 +2158,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/10/02 00:00:05</t>
+          <t>2026/10/01 02:49:02</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-03 00:00:05</t>
+          <t>2026-10-02 00:00:05</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2131,19 +2180,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/10/03 00:00:05</t>
+          <t>2026/10/02 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-04 00:00:05</t>
+          <t>2026-10-03 00:00:05</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2153,19 +2202,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026/10/04 00:00:05</t>
+          <t>2026/10/03 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-05 00:00:05</t>
+          <t>2026-10-04 00:00:05</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2175,19 +2224,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/10/05 00:00:05</t>
+          <t>2026/10/04 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 00:00:05</t>
+          <t>2026-10-05 00:00:05</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2197,34 +2246,78 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/10/06 00:00:05</t>
+          <t>2026/10/05 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-10-06 00:00:05</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026/10/06 00:00:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>2026-10-07 00:00:05</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>673.51</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>2026/10/07 00:00:05</t>
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-10-08 00:00:05</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026/10/08 00:00:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E10"/>
+  <autoFilter ref="A1:E11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1900,8 +1900,60 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-10-08 07:19:56</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>669.48</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>669.48</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>672.29</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>672.29</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026/10/08 07:19:56</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-10-07 23:53:04</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J28"/>
+  <autoFilter ref="A1:J29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2097,7 +2149,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
         <v>673.51</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1952,8 +1952,60 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:06:52</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>669.3</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>669.3</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>672.11</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>672.11</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>673.67</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026/10/08 12:06:52</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-10-08 04:11:58</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J29"/>
+  <autoFilter ref="A1:J30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2149,16 +2201,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>673.51</v>
+        <v>673.5633</v>
       </c>
       <c r="D11" t="n">
         <v>673.51</v>
       </c>
       <c r="E11" t="n">
-        <v>673.51</v>
+        <v>673.67</v>
       </c>
     </row>
     <row r="12"/>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2004,8 +2004,60 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:21:54</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>669.39</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>669.39</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>672.2</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>672.2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>673.67</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026/10/08 19:21:54</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:23:41</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2201,10 +2253,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>673.5633</v>
+        <v>673.59</v>
       </c>
       <c r="D11" t="n">
         <v>673.51</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2056,8 +2056,60 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-10-09 01:51:55</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>669.39</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>669.39</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>672.2</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>672.2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>673.67</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026/10/09 01:51:55</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-10-08 17:56:30</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:J32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2068,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2265,68 +2317,65 @@
         <v>673.67</v>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>673.67</v>
+      </c>
+      <c r="D12" t="n">
+        <v>673.67</v>
+      </c>
+      <c r="E12" t="n">
+        <v>673.67</v>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-01 02:49:02</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>673.51</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/10/01 02:49:02</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:05</t>
+          <t>2026-10-01 02:49:02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2336,19 +2385,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/10/02 00:00:05</t>
+          <t>2026/10/01 02:49:02</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-03 00:00:05</t>
+          <t>2026-10-02 00:00:05</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2358,19 +2407,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026/10/03 00:00:05</t>
+          <t>2026/10/02 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-04 00:00:05</t>
+          <t>2026-10-03 00:00:05</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2380,19 +2429,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/10/04 00:00:05</t>
+          <t>2026/10/03 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-05 00:00:05</t>
+          <t>2026-10-04 00:00:05</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2402,19 +2451,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/10/05 00:00:05</t>
+          <t>2026/10/04 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 00:00:05</t>
+          <t>2026-10-05 00:00:05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2424,19 +2473,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026/10/06 00:00:05</t>
+          <t>2026/10/05 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-07 00:00:05</t>
+          <t>2026-10-06 00:00:05</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2446,34 +2495,78 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/10/07 00:00:05</t>
+          <t>2026/10/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:00:05</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026/10/07 00:00:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>2026-10-08 00:00:05</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>673.51</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>2026/10/08 00:00:05</t>
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-10-09 01:51:55</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>673.67</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026/10/09 01:51:55</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E11"/>
+  <autoFilter ref="A1:E12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2108,8 +2108,60 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-10-09 06:40:26</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>669.38</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>669.38</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>672.19</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>672.19</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>673.67</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026/10/09 06:40:26</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-10-08 23:07:59</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J32"/>
+  <autoFilter ref="A1:J33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2324,7 +2376,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
         <v>673.67</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2160,8 +2160,60 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-10-09 10:51:57</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>668.67</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>668.67</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>671.48</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>671.48</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>673.3</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2026/10/09 10:51:57</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-10-09 02:55:51</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J33"/>
+  <autoFilter ref="A1:J34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2376,13 +2428,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>673.67</v>
+        <v>673.5467</v>
       </c>
       <c r="D12" t="n">
-        <v>673.67</v>
+        <v>673.3</v>
       </c>
       <c r="E12" t="n">
         <v>673.67</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2212,8 +2212,60 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-10-09 18:11:59</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>668.15</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>668.15</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>670.96</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>670.96</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>673.3</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2026/10/09 18:11:59</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-10-09 10:13:04</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J34"/>
+  <autoFilter ref="A1:J35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2428,10 +2480,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>673.5467</v>
+        <v>673.485</v>
       </c>
       <c r="D12" t="n">
         <v>673.3</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2264,8 +2264,60 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-10-10 00:57:17</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>668.2</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>668.2</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>671.01</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>671.01</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>673.3</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026/10/10 00:57:17</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:00:58</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J35"/>
+  <autoFilter ref="A1:J36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2276,7 +2328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2492,68 +2544,65 @@
         <v>673.67</v>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>673.3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>673.3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>673.3</v>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-01 02:49:02</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>673.51</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/10/01 02:49:02</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:05</t>
+          <t>2026-10-01 02:49:02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2563,19 +2612,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026/10/02 00:00:05</t>
+          <t>2026/10/01 02:49:02</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-03 00:00:05</t>
+          <t>2026-10-02 00:00:05</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2585,19 +2634,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/10/03 00:00:05</t>
+          <t>2026/10/02 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-04 00:00:05</t>
+          <t>2026-10-03 00:00:05</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2607,19 +2656,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/10/04 00:00:05</t>
+          <t>2026/10/03 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-05 00:00:05</t>
+          <t>2026-10-04 00:00:05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2629,19 +2678,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026/10/05 00:00:05</t>
+          <t>2026/10/04 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 00:00:05</t>
+          <t>2026-10-05 00:00:05</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2651,19 +2700,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/10/06 00:00:05</t>
+          <t>2026/10/05 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-07 00:00:05</t>
+          <t>2026-10-06 00:00:05</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2673,19 +2722,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/10/07 00:00:05</t>
+          <t>2026/10/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-08 00:00:05</t>
+          <t>2026-10-07 00:00:05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2695,34 +2744,78 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/10/08 00:00:05</t>
+          <t>2026/10/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-10-08 00:00:05</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>673.51</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026/10/08 00:00:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>2026-10-09 01:51:55</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>673.67</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>2026/10/09 01:51:55</t>
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-10-10 00:57:17</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>673.3</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026/10/10 00:57:17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E12"/>
+  <autoFilter ref="A1:E13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2316,8 +2316,60 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-10-10 05:30:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>668.3</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>668.3</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>671.11</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>671.11</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>673.3</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026/10/10 05:30:00</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-10-09 21:36:02</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J36"/>
+  <autoFilter ref="A1:J37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2551,7 +2603,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
         <v>673.3</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2368,8 +2368,60 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-10-10 14:18:13</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>667.43</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>667.43</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>670.24</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>670.24</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>673.3</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026/10/10 14:18:13</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-10-10 07:14:25</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J37"/>
+  <autoFilter ref="A1:J38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2603,7 +2655,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
         <v>673.3</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2420,8 +2420,60 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-10-10 17:39:13</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>668.3</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>668.3</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>671.11</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>671.11</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>673.3</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026/10/10 17:39:13</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-10-10 13:49:04</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J38"/>
+  <autoFilter ref="A1:J39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2655,7 +2707,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
         <v>673.3</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2472,8 +2472,60 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-10-11 00:00:05</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>668.3</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>668.3</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>671.11</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>671.11</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>673.3</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2026/10/11 00:00:05</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-10-10 18:04:38</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J39"/>
+  <autoFilter ref="A1:J40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2484,7 +2536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2719,68 +2771,65 @@
         <v>673.3</v>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>673.3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>673.3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>673.3</v>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-01 02:49:02</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>673.51</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026/10/01 02:49:02</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:05</t>
+          <t>2026-10-01 02:49:02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2790,19 +2839,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/10/02 00:00:05</t>
+          <t>2026/10/01 02:49:02</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-03 00:00:05</t>
+          <t>2026-10-02 00:00:05</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2812,19 +2861,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/10/03 00:00:05</t>
+          <t>2026/10/02 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-04 00:00:05</t>
+          <t>2026-10-03 00:00:05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2834,19 +2883,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026/10/04 00:00:05</t>
+          <t>2026/10/03 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-05 00:00:05</t>
+          <t>2026-10-04 00:00:05</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2856,19 +2905,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/10/05 00:00:05</t>
+          <t>2026/10/04 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 00:00:05</t>
+          <t>2026-10-05 00:00:05</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2878,19 +2927,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/10/06 00:00:05</t>
+          <t>2026/10/05 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-07 00:00:05</t>
+          <t>2026-10-06 00:00:05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2900,19 +2949,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/10/07 00:00:05</t>
+          <t>2026/10/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-08 00:00:05</t>
+          <t>2026-10-07 00:00:05</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2922,56 +2971,100 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/10/08 00:00:05</t>
+          <t>2026/10/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-09 01:51:55</t>
+          <t>2026-10-08 00:00:05</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>673.67</t>
+          <t>673.51</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/10/09 01:51:55</t>
+          <t>2026/10/08 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-10-09 01:51:55</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>673.67</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026/10/09 01:51:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>2026-10-10 00:57:17</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>673.3</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>2026/10/10 00:57:17</t>
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-10-11 00:00:05</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>673.3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026/10/11 00:00:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E13"/>
+  <autoFilter ref="A1:E14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2524,8 +2524,60 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-10-11 05:30:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>668.3</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>668.3</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>671.11</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>671.11</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>673.3</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2026/10/11 05:30:00</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-10-10 21:36:46</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J40"/>
+  <autoFilter ref="A1:J41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2778,7 +2830,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
         <v>673.3</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2576,8 +2576,60 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-10-11 10:30:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>668.3</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>668.3</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>671.11</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>671.11</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>673.3</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2026/10/11 10:30:00</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-10-11 06:18:24</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J41"/>
+  <autoFilter ref="A1:J42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2830,7 +2882,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
         <v>673.3</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2628,8 +2628,60 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:00:05</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>668.3</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>668.3</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>671.11</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>671.11</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>673.3</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2026/10/12 00:00:05</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-10-11 18:02:40</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J42"/>
+  <autoFilter ref="A1:J43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2640,7 +2692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2894,68 +2946,65 @@
         <v>673.3</v>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>673.3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>673.3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>673.3</v>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-01 02:49:02</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>673.51</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/10/01 02:49:02</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:05</t>
+          <t>2026-10-01 02:49:02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2965,19 +3014,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/10/02 00:00:05</t>
+          <t>2026/10/01 02:49:02</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-03 00:00:05</t>
+          <t>2026-10-02 00:00:05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2987,19 +3036,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026/10/03 00:00:05</t>
+          <t>2026/10/02 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-04 00:00:05</t>
+          <t>2026-10-03 00:00:05</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3009,19 +3058,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/10/04 00:00:05</t>
+          <t>2026/10/03 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-05 00:00:05</t>
+          <t>2026-10-04 00:00:05</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3031,19 +3080,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/10/05 00:00:05</t>
+          <t>2026/10/04 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 00:00:05</t>
+          <t>2026-10-05 00:00:05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3053,19 +3102,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/10/06 00:00:05</t>
+          <t>2026/10/05 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-07 00:00:05</t>
+          <t>2026-10-06 00:00:05</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3075,19 +3124,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/10/07 00:00:05</t>
+          <t>2026/10/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-08 00:00:05</t>
+          <t>2026-10-07 00:00:05</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3097,78 +3146,122 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/10/08 00:00:05</t>
+          <t>2026/10/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-09 01:51:55</t>
+          <t>2026-10-08 00:00:05</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>673.67</t>
+          <t>673.51</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/10/09 01:51:55</t>
+          <t>2026/10/08 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-10 00:57:17</t>
+          <t>2026-10-09 01:51:55</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>673.67</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/10/10 00:57:17</t>
+          <t>2026/10/09 01:51:55</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-10-10 00:57:17</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>673.3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026/10/10 00:57:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>2026-10-11 00:00:05</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>673.3</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>2026/10/11 00:00:05</t>
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:00:05</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>673.3</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026/10/12 00:00:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E14"/>
+  <autoFilter ref="A1:E15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2680,8 +2680,60 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-10-12 05:30:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>668.3</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>668.3</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>671.11</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>671.11</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>673.3</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2026/10/12 05:30:00</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-10-11 21:50:46</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J43"/>
+  <autoFilter ref="A1:J44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2953,7 +3005,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
         <v>673.3</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2732,8 +2732,60 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-10-12 07:55:42</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>668.3</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>668.3</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>671.11</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>671.11</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>673.3</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2026/10/12 07:55:42</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:48:18</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J44"/>
+  <autoFilter ref="A1:J45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3005,7 +3057,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
         <v>673.3</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2784,8 +2784,60 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:37:16</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>668.06</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>668.06</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>670.87</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>670.87</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>673.13</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2026/10/12 14:37:16</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:38:18</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J45"/>
+  <autoFilter ref="A1:J46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3057,13 +3109,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>673.3</v>
+        <v>673.2575000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>673.3</v>
+        <v>673.13</v>
       </c>
       <c r="E15" t="n">
         <v>673.3</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2836,8 +2836,60 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-10-13 00:03:04</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>668.21</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>668.21</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>671.02</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>671.02</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>673.13</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2026/10/13 00:03:04</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:07:16</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J46"/>
+  <autoFilter ref="A1:J47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2848,7 +2900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3121,68 +3173,65 @@
         <v>673.3</v>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>673.13</v>
+      </c>
+      <c r="D16" t="n">
+        <v>673.13</v>
+      </c>
+      <c r="E16" t="n">
+        <v>673.13</v>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-01 02:49:02</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>673.51</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/10/01 02:49:02</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:05</t>
+          <t>2026-10-01 02:49:02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3192,19 +3241,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026/10/02 00:00:05</t>
+          <t>2026/10/01 02:49:02</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-03 00:00:05</t>
+          <t>2026-10-02 00:00:05</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3214,19 +3263,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/10/03 00:00:05</t>
+          <t>2026/10/02 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-04 00:00:05</t>
+          <t>2026-10-03 00:00:05</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3236,19 +3285,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/10/04 00:00:05</t>
+          <t>2026/10/03 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-05 00:00:05</t>
+          <t>2026-10-04 00:00:05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3258,19 +3307,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/10/05 00:00:05</t>
+          <t>2026/10/04 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 00:00:05</t>
+          <t>2026-10-05 00:00:05</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3280,19 +3329,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/10/06 00:00:05</t>
+          <t>2026/10/05 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-07 00:00:05</t>
+          <t>2026-10-06 00:00:05</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3302,19 +3351,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/10/07 00:00:05</t>
+          <t>2026/10/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-08 00:00:05</t>
+          <t>2026-10-07 00:00:05</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3324,63 +3373,63 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/10/08 00:00:05</t>
+          <t>2026/10/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-09 01:51:55</t>
+          <t>2026-10-08 00:00:05</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>673.67</t>
+          <t>673.51</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/10/09 01:51:55</t>
+          <t>2026/10/08 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-10 00:57:17</t>
+          <t>2026-10-09 01:51:55</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>673.67</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/10/10 00:57:17</t>
+          <t>2026/10/09 01:51:55</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-11 00:00:05</t>
+          <t>2026-10-10 00:57:17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3390,34 +3439,78 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/10/11 00:00:05</t>
+          <t>2026/10/10 00:57:17</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-10-11 00:00:05</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>673.3</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026/10/11 00:00:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>2026-10-12 00:00:05</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>673.3</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>2026/10/12 00:00:05</t>
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-10-13 00:03:04</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>673.13</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026/10/13 00:03:04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E15"/>
+  <autoFilter ref="A1:E16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2888,8 +2888,60 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-10-13 05:30:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>668.31</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>668.31</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>671.12</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>671.12</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>673.13</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2026/10/13 05:30:00</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-10-12 22:56:01</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J47"/>
+  <autoFilter ref="A1:J48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3180,7 +3232,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
         <v>673.13</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2940,8 +2940,60 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-10-13 11:22:20</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>668.52</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>668.52</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>671.33</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>671.33</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>672.98</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2026/10/13 11:22:20</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2026-10-13 03:24:30</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J48"/>
+  <autoFilter ref="A1:J49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3232,13 +3284,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>673.13</v>
+        <v>673.08</v>
       </c>
       <c r="D16" t="n">
-        <v>673.13</v>
+        <v>672.98</v>
       </c>
       <c r="E16" t="n">
         <v>673.13</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2992,8 +2992,60 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-10-13 18:47:22</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>668.22</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>668.22</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>671.03</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>671.03</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>672.98</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2026/10/13 18:47:22</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:54:02</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J49"/>
+  <autoFilter ref="A1:J50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3284,10 +3336,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>673.08</v>
+        <v>673.0549999999999</v>
       </c>
       <c r="D16" t="n">
         <v>672.98</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3044,8 +3044,60 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-10-14 01:52:24</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>668.08</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>668.08</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>670.89</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>670.89</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>672.98</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2026/10/14 01:52:24</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:55:51</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J50"/>
+  <autoFilter ref="A1:J51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3056,7 +3108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3348,68 +3400,65 @@
         <v>673.13</v>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>672.98</v>
+      </c>
+      <c r="D17" t="n">
+        <v>672.98</v>
+      </c>
+      <c r="E17" t="n">
+        <v>672.98</v>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-01 02:49:02</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>673.51</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026/10/01 02:49:02</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:05</t>
+          <t>2026-10-01 02:49:02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3419,19 +3468,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/10/02 00:00:05</t>
+          <t>2026/10/01 02:49:02</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-03 00:00:05</t>
+          <t>2026-10-02 00:00:05</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3441,19 +3490,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/10/03 00:00:05</t>
+          <t>2026/10/02 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-04 00:00:05</t>
+          <t>2026-10-03 00:00:05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3463,19 +3512,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/10/04 00:00:05</t>
+          <t>2026/10/03 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-05 00:00:05</t>
+          <t>2026-10-04 00:00:05</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3485,19 +3534,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/10/05 00:00:05</t>
+          <t>2026/10/04 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 00:00:05</t>
+          <t>2026-10-05 00:00:05</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3507,19 +3556,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/10/06 00:00:05</t>
+          <t>2026/10/05 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-07 00:00:05</t>
+          <t>2026-10-06 00:00:05</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3529,19 +3578,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/10/07 00:00:05</t>
+          <t>2026/10/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-08 00:00:05</t>
+          <t>2026-10-07 00:00:05</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3551,63 +3600,63 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/10/08 00:00:05</t>
+          <t>2026/10/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-09 01:51:55</t>
+          <t>2026-10-08 00:00:05</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>673.67</t>
+          <t>673.51</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/10/09 01:51:55</t>
+          <t>2026/10/08 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-10 00:57:17</t>
+          <t>2026-10-09 01:51:55</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>673.67</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/10/10 00:57:17</t>
+          <t>2026/10/09 01:51:55</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-11 00:00:05</t>
+          <t>2026-10-10 00:57:17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3617,19 +3666,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/10/11 00:00:05</t>
+          <t>2026/10/10 00:57:17</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:05</t>
+          <t>2026-10-11 00:00:05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3639,34 +3688,78 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/10/12 00:00:05</t>
+          <t>2026/10/11 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:00:05</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>673.3</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026/10/12 00:00:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>2026-10-13 00:03:04</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>673.13</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>2026/10/13 00:03:04</t>
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-10-14 01:52:24</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>672.98</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026/10/14 01:52:24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E16"/>
+  <autoFilter ref="A1:E17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3096,8 +3096,60 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-10-14 05:30:00</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>668.17</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>668.17</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>670.98</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>670.98</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>672.98</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2026/10/14 05:30:00</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-10-13 22:24:40</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J51"/>
+  <autoFilter ref="A1:J52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3407,7 +3459,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
         <v>672.98</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3148,8 +3148,60 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:16:01</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>668.17</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>668.17</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>670.98</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>670.98</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>672.49</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2026/10/14 09:16:01</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-10-14 01:19:06</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J52"/>
+  <autoFilter ref="A1:J53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3459,13 +3511,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>672.98</v>
+        <v>672.8167</v>
       </c>
       <c r="D17" t="n">
-        <v>672.98</v>
+        <v>672.49</v>
       </c>
       <c r="E17" t="n">
         <v>672.98</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3200,8 +3200,60 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:12:27</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>668.08</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>668.08</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>670.89</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>670.89</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>672.49</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2026/10/14 14:12:27</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-10-14 06:15:18</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J53"/>
+  <autoFilter ref="A1:J54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3511,10 +3563,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>672.8167</v>
+        <v>672.735</v>
       </c>
       <c r="D17" t="n">
         <v>672.49</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3252,8 +3252,60 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-10-14 20:02:28</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>668.18</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>668.18</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>670.99</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>670.99</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>672.49</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2026/10/14 20:02:28</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:04:28</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J54"/>
+  <autoFilter ref="A1:J55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3563,10 +3615,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>672.735</v>
+        <v>672.686</v>
       </c>
       <c r="D17" t="n">
         <v>672.49</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$55</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3304,8 +3304,60 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-10-15 01:02:29</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>668.67</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>668.67</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>671.48</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>671.48</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>672.49</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2026/10/15 01:02:29</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2026-10-14 17:04:12</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J55"/>
+  <autoFilter ref="A1:J56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3316,7 +3368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3627,68 +3679,65 @@
         <v>672.98</v>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>672.49</v>
+      </c>
+      <c r="D18" t="n">
+        <v>672.49</v>
+      </c>
+      <c r="E18" t="n">
+        <v>672.49</v>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-01 02:49:02</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>673.51</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/10/01 02:49:02</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:05</t>
+          <t>2026-10-01 02:49:02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3698,19 +3747,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/10/02 00:00:05</t>
+          <t>2026/10/01 02:49:02</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-03 00:00:05</t>
+          <t>2026-10-02 00:00:05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3720,19 +3769,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/10/03 00:00:05</t>
+          <t>2026/10/02 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-04 00:00:05</t>
+          <t>2026-10-03 00:00:05</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3742,19 +3791,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/10/04 00:00:05</t>
+          <t>2026/10/03 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-05 00:00:05</t>
+          <t>2026-10-04 00:00:05</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3764,19 +3813,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/10/05 00:00:05</t>
+          <t>2026/10/04 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 00:00:05</t>
+          <t>2026-10-05 00:00:05</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3786,19 +3835,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/10/06 00:00:05</t>
+          <t>2026/10/05 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-07 00:00:05</t>
+          <t>2026-10-06 00:00:05</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3808,19 +3857,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/10/07 00:00:05</t>
+          <t>2026/10/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-08 00:00:05</t>
+          <t>2026-10-07 00:00:05</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3830,63 +3879,63 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/10/08 00:00:05</t>
+          <t>2026/10/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-09 01:51:55</t>
+          <t>2026-10-08 00:00:05</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>673.67</t>
+          <t>673.51</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/10/09 01:51:55</t>
+          <t>2026/10/08 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-10 00:57:17</t>
+          <t>2026-10-09 01:51:55</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>673.67</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/10/10 00:57:17</t>
+          <t>2026/10/09 01:51:55</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-11 00:00:05</t>
+          <t>2026-10-10 00:57:17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3896,19 +3945,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/10/11 00:00:05</t>
+          <t>2026/10/10 00:57:17</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:05</t>
+          <t>2026-10-11 00:00:05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3918,56 +3967,100 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/10/12 00:00:05</t>
+          <t>2026/10/11 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-13 00:03:04</t>
+          <t>2026-10-12 00:00:05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>673.13</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/10/13 00:03:04</t>
+          <t>2026/10/12 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-10-13 00:03:04</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>673.13</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026/10/13 00:03:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>2026-10-14 01:52:24</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>672.98</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>2026/10/14 01:52:24</t>
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-10-15 01:02:29</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>672.49</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026/10/15 01:02:29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E17"/>
+  <autoFilter ref="A1:E18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3356,8 +3356,60 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-10-15 02:48:45</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>668.76</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>668.76</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>671.57</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>671.57</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>672.49</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2026/10/15 02:48:45</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-10-14 20:39:01</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J56"/>
+  <autoFilter ref="A1:J57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3686,7 +3738,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>672.49</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3408,8 +3408,60 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:40:34</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>668.76</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>668.76</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>671.57</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>671.57</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>672.49</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2026/10/15 06:40:34</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2026-10-14 23:26:50</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J57"/>
+  <autoFilter ref="A1:J58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3738,7 +3790,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
         <v>672.49</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3460,8 +3460,60 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:37:31</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>668.27</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>668.27</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>671.08</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>671.08</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>672.53</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2026/10/15 09:37:31</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2026-10-15 01:42:57</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J58"/>
+  <autoFilter ref="A1:J59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3790,16 +3842,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>672.49</v>
+        <v>672.5</v>
       </c>
       <c r="D18" t="n">
         <v>672.49</v>
       </c>
       <c r="E18" t="n">
-        <v>672.49</v>
+        <v>672.53</v>
       </c>
     </row>
     <row r="19"/>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3512,8 +3512,60 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:27:32</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>668.17</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>668.17</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>670.98</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>670.98</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>672.53</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2026/10/15 14:27:32</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:30:16</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J59"/>
+  <autoFilter ref="A1:J60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3842,10 +3894,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>672.5</v>
+        <v>672.506</v>
       </c>
       <c r="D18" t="n">
         <v>672.49</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3564,8 +3564,60 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-10-15 19:57:34</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>668.1</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>668.1</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>670.91</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>670.91</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>672.53</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2026/10/15 19:57:34</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2026-10-15 11:59:55</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J60"/>
+  <autoFilter ref="A1:J61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3894,10 +3946,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>672.506</v>
+        <v>672.51</v>
       </c>
       <c r="D18" t="n">
         <v>672.49</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3616,8 +3616,60 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:47:35</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>668.04</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>668.04</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>670.85</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>670.85</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>672.53</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2026/10/16 00:47:35</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2026-10-15 16:50:05</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J61"/>
+  <autoFilter ref="A1:J62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3628,7 +3680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3958,68 +4010,65 @@
         <v>672.53</v>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>672.53</v>
+      </c>
+      <c r="D19" t="n">
+        <v>672.53</v>
+      </c>
+      <c r="E19" t="n">
+        <v>672.53</v>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-01 02:49:02</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>673.51</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/10/01 02:49:02</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:05</t>
+          <t>2026-10-01 02:49:02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4029,19 +4078,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/10/02 00:00:05</t>
+          <t>2026/10/01 02:49:02</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-03 00:00:05</t>
+          <t>2026-10-02 00:00:05</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4051,19 +4100,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/10/03 00:00:05</t>
+          <t>2026/10/02 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-04 00:00:05</t>
+          <t>2026-10-03 00:00:05</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4073,19 +4122,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/10/04 00:00:05</t>
+          <t>2026/10/03 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-05 00:00:05</t>
+          <t>2026-10-04 00:00:05</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4095,19 +4144,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/10/05 00:00:05</t>
+          <t>2026/10/04 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 00:00:05</t>
+          <t>2026-10-05 00:00:05</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4117,19 +4166,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/10/06 00:00:05</t>
+          <t>2026/10/05 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-07 00:00:05</t>
+          <t>2026-10-06 00:00:05</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4139,19 +4188,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/10/07 00:00:05</t>
+          <t>2026/10/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-08 00:00:05</t>
+          <t>2026-10-07 00:00:05</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4161,63 +4210,63 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/10/08 00:00:05</t>
+          <t>2026/10/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-09 01:51:55</t>
+          <t>2026-10-08 00:00:05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>673.67</t>
+          <t>673.51</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/10/09 01:51:55</t>
+          <t>2026/10/08 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-10 00:57:17</t>
+          <t>2026-10-09 01:51:55</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>673.67</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/10/10 00:57:17</t>
+          <t>2026/10/09 01:51:55</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-11 00:00:05</t>
+          <t>2026-10-10 00:57:17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4227,19 +4276,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/10/11 00:00:05</t>
+          <t>2026/10/10 00:57:17</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:05</t>
+          <t>2026-10-11 00:00:05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4249,78 +4298,122 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/10/12 00:00:05</t>
+          <t>2026/10/11 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-13 00:03:04</t>
+          <t>2026-10-12 00:00:05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>673.13</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/10/13 00:03:04</t>
+          <t>2026/10/12 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 01:52:24</t>
+          <t>2026-10-13 00:03:04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>672.98</t>
+          <t>673.13</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/10/14 01:52:24</t>
+          <t>2026/10/13 00:03:04</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-10-14 01:52:24</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>672.98</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026/10/14 01:52:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>2026-10-15 01:02:29</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>672.49</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>2026/10/15 01:02:29</t>
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:47:35</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>672.53</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026/10/16 00:47:35</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E18"/>
+  <autoFilter ref="A1:E19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3668,8 +3668,60 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-10-16 02:54:05</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>668.13</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>668.13</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>670.94</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>670.94</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>672.53</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2026/10/16 02:54:05</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2026-10-15 20:05:08</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J62"/>
+  <autoFilter ref="A1:J63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4017,7 +4069,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>672.53</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3720,8 +3720,60 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:50:13</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>668.13</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>668.13</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>670.94</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>670.94</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>672.53</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2026/10/16 06:50:13</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2026-10-15 23:01:25</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J63"/>
+  <autoFilter ref="A1:J64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4069,7 +4121,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
         <v>672.53</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3772,8 +3772,60 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-10-16 07:57:17</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>668.13</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>668.13</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>670.94</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>670.94</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>672.53</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2026/10/16 07:57:17</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2026-10-16 01:12:22</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J64"/>
+  <autoFilter ref="A1:J65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4121,7 +4173,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
         <v>672.53</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3824,8 +3824,60 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:47:38</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>667.84</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>667.84</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>670.65</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>670.65</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>672.2</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2026/10/16 13:47:38</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2026-10-16 05:53:37</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J65"/>
+  <autoFilter ref="A1:J66"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4173,13 +4225,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>672.53</v>
+        <v>672.4640000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>672.53</v>
+        <v>672.2</v>
       </c>
       <c r="E19" t="n">
         <v>672.53</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3876,8 +3876,60 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-10-16 18:37:39</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>667.51</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>667.51</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>670.32</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>670.32</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>672.2</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2026/10/16 18:37:39</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:38:58</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J66"/>
+  <autoFilter ref="A1:J67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4225,10 +4277,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>672.4640000000001</v>
+        <v>672.42</v>
       </c>
       <c r="D19" t="n">
         <v>672.2</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$68</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3928,8 +3928,60 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-10-16 22:57:40</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>667.55</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>667.55</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>670.36</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>670.36</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>672.2</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2026/10/16 22:57:40</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2026-10-16 15:00:07</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J67"/>
+  <autoFilter ref="A1:J68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4277,10 +4329,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>672.42</v>
+        <v>672.3886</v>
       </c>
       <c r="D19" t="n">
         <v>672.2</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$68</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3980,8 +3980,60 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-10-17 02:42:41</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>667.6</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>667.6</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>670.41</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>670.41</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>672.2</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2026/10/17 02:42:41</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2026-10-16 18:44:33</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J68"/>
+  <autoFilter ref="A1:J69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3992,7 +4044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4341,68 +4393,65 @@
         <v>672.53</v>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>672.2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>672.2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>672.2</v>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-01 02:49:02</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>673.51</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/10/01 02:49:02</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:05</t>
+          <t>2026-10-01 02:49:02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4412,19 +4461,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/10/02 00:00:05</t>
+          <t>2026/10/01 02:49:02</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-03 00:00:05</t>
+          <t>2026-10-02 00:00:05</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4434,19 +4483,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/10/03 00:00:05</t>
+          <t>2026/10/02 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-04 00:00:05</t>
+          <t>2026-10-03 00:00:05</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4456,19 +4505,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/10/04 00:00:05</t>
+          <t>2026/10/03 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-05 00:00:05</t>
+          <t>2026-10-04 00:00:05</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4478,19 +4527,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/10/05 00:00:05</t>
+          <t>2026/10/04 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 00:00:05</t>
+          <t>2026-10-05 00:00:05</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4500,19 +4549,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/10/06 00:00:05</t>
+          <t>2026/10/05 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-07 00:00:05</t>
+          <t>2026-10-06 00:00:05</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4522,19 +4571,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/10/07 00:00:05</t>
+          <t>2026/10/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-08 00:00:05</t>
+          <t>2026-10-07 00:00:05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4544,63 +4593,63 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/10/08 00:00:05</t>
+          <t>2026/10/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-09 01:51:55</t>
+          <t>2026-10-08 00:00:05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>673.67</t>
+          <t>673.51</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/10/09 01:51:55</t>
+          <t>2026/10/08 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-10 00:57:17</t>
+          <t>2026-10-09 01:51:55</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>673.67</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/10/10 00:57:17</t>
+          <t>2026/10/09 01:51:55</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-11 00:00:05</t>
+          <t>2026-10-10 00:57:17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4610,19 +4659,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/10/11 00:00:05</t>
+          <t>2026/10/10 00:57:17</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:05</t>
+          <t>2026-10-11 00:00:05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4632,100 +4681,144 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/10/12 00:00:05</t>
+          <t>2026/10/11 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-13 00:03:04</t>
+          <t>2026-10-12 00:00:05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>673.13</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/10/13 00:03:04</t>
+          <t>2026/10/12 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 01:52:24</t>
+          <t>2026-10-13 00:03:04</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>672.98</t>
+          <t>673.13</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/10/14 01:52:24</t>
+          <t>2026/10/13 00:03:04</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-15 01:02:29</t>
+          <t>2026-10-14 01:52:24</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>672.49</t>
+          <t>672.98</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/10/15 01:02:29</t>
+          <t>2026/10/14 01:52:24</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-10-15 01:02:29</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>672.49</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026/10/15 01:02:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>2026-10-16 00:47:35</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>672.53</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>2026/10/16 00:47:35</t>
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-10-17 02:42:41</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>672.2</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026/10/17 02:42:41</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E19"/>
+  <autoFilter ref="A1:E20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4032,8 +4032,60 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-10-17 05:30:00</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>667.68</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>667.68</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>670.49</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>670.49</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>672.2</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2026/10/17 05:30:00</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:45:38</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J69"/>
+  <autoFilter ref="A1:J70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4400,7 +4452,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
         <v>672.2</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4084,8 +4084,60 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-10-17 10:30:00</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>667.68</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>667.68</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>670.49</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>670.49</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>672.2</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2026/10/17 10:30:00</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2026-10-17 04:03:28</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J70"/>
+  <autoFilter ref="A1:J71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4452,7 +4504,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
         <v>672.2</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$71</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4136,8 +4136,60 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-10-18 00:00:05</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>667.68</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>667.68</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>670.49</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>670.49</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>672.2</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2026/10/18 00:00:05</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2026-10-17 17:57:58</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J71"/>
+  <autoFilter ref="A1:J72"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4148,7 +4200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4516,68 +4568,65 @@
         <v>672.2</v>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>672.2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>672.2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>672.2</v>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-01 02:49:02</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>673.51</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/10/01 02:49:02</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:05</t>
+          <t>2026-10-01 02:49:02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4587,19 +4636,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/10/02 00:00:05</t>
+          <t>2026/10/01 02:49:02</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-03 00:00:05</t>
+          <t>2026-10-02 00:00:05</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4609,19 +4658,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/10/03 00:00:05</t>
+          <t>2026/10/02 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-04 00:00:05</t>
+          <t>2026-10-03 00:00:05</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4631,19 +4680,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/10/04 00:00:05</t>
+          <t>2026/10/03 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-05 00:00:05</t>
+          <t>2026-10-04 00:00:05</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4653,19 +4702,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/10/05 00:00:05</t>
+          <t>2026/10/04 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 00:00:05</t>
+          <t>2026-10-05 00:00:05</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4675,19 +4724,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/10/06 00:00:05</t>
+          <t>2026/10/05 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-07 00:00:05</t>
+          <t>2026-10-06 00:00:05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4697,19 +4746,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/10/07 00:00:05</t>
+          <t>2026/10/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-08 00:00:05</t>
+          <t>2026-10-07 00:00:05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4719,63 +4768,63 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/10/08 00:00:05</t>
+          <t>2026/10/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-09 01:51:55</t>
+          <t>2026-10-08 00:00:05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>673.67</t>
+          <t>673.51</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/10/09 01:51:55</t>
+          <t>2026/10/08 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-10 00:57:17</t>
+          <t>2026-10-09 01:51:55</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>673.67</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/10/10 00:57:17</t>
+          <t>2026/10/09 01:51:55</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-11 00:00:05</t>
+          <t>2026-10-10 00:57:17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4785,19 +4834,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/10/11 00:00:05</t>
+          <t>2026/10/10 00:57:17</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:05</t>
+          <t>2026-10-11 00:00:05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4807,122 +4856,166 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/10/12 00:00:05</t>
+          <t>2026/10/11 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-13 00:03:04</t>
+          <t>2026-10-12 00:00:05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>673.13</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/10/13 00:03:04</t>
+          <t>2026/10/12 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 01:52:24</t>
+          <t>2026-10-13 00:03:04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>672.98</t>
+          <t>673.13</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/10/14 01:52:24</t>
+          <t>2026/10/13 00:03:04</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-15 01:02:29</t>
+          <t>2026-10-14 01:52:24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>672.49</t>
+          <t>672.98</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/10/15 01:02:29</t>
+          <t>2026/10/14 01:52:24</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-16 00:47:35</t>
+          <t>2026-10-15 01:02:29</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>672.53</t>
+          <t>672.49</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/10/16 00:47:35</t>
+          <t>2026/10/15 01:02:29</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:47:35</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>672.53</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026/10/16 00:47:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>2026-10-17 02:42:41</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>672.2</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>2026/10/17 02:42:41</t>
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-10-18 00:00:05</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>672.2</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026/10/18 00:00:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E20"/>
+  <autoFilter ref="A1:E21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4188,8 +4188,60 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-10-18 05:30:00</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>667.68</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>667.68</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>670.49</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>670.49</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>672.2</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2026/10/18 05:30:00</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2026-10-17 22:34:26</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J72"/>
+  <autoFilter ref="A1:J73"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4575,7 +4627,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
         <v>672.2</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$74</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4240,8 +4240,60 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-10-18 10:30:00</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>667.68</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>667.68</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>670.49</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>670.49</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>672.2</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2026/10/18 10:30:00</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:44:14</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J73"/>
+  <autoFilter ref="A1:J74"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4627,7 +4679,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
         <v>672.2</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$74</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4292,8 +4292,60 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-10-19 00:00:05</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>667.68</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>667.68</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>670.49</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>670.49</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>672.2</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2026/10/19 00:00:05</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2026-10-18 16:35:38</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J74"/>
+  <autoFilter ref="A1:J75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4304,7 +4356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4691,68 +4743,65 @@
         <v>672.2</v>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>672.2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>672.2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>672.2</v>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-01 02:49:02</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>673.51</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/10/01 02:49:02</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:05</t>
+          <t>2026-10-01 02:49:02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4762,19 +4811,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/10/02 00:00:05</t>
+          <t>2026/10/01 02:49:02</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-03 00:00:05</t>
+          <t>2026-10-02 00:00:05</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4784,19 +4833,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/10/03 00:00:05</t>
+          <t>2026/10/02 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-04 00:00:05</t>
+          <t>2026-10-03 00:00:05</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4806,19 +4855,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/10/04 00:00:05</t>
+          <t>2026/10/03 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-05 00:00:05</t>
+          <t>2026-10-04 00:00:05</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4828,19 +4877,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/10/05 00:00:05</t>
+          <t>2026/10/04 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 00:00:05</t>
+          <t>2026-10-05 00:00:05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4850,19 +4899,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/10/06 00:00:05</t>
+          <t>2026/10/05 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-07 00:00:05</t>
+          <t>2026-10-06 00:00:05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4872,19 +4921,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/10/07 00:00:05</t>
+          <t>2026/10/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-08 00:00:05</t>
+          <t>2026-10-07 00:00:05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4894,63 +4943,63 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/10/08 00:00:05</t>
+          <t>2026/10/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-09 01:51:55</t>
+          <t>2026-10-08 00:00:05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>673.67</t>
+          <t>673.51</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/10/09 01:51:55</t>
+          <t>2026/10/08 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-10 00:57:17</t>
+          <t>2026-10-09 01:51:55</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>673.67</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/10/10 00:57:17</t>
+          <t>2026/10/09 01:51:55</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-11 00:00:05</t>
+          <t>2026-10-10 00:57:17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4960,19 +5009,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/10/11 00:00:05</t>
+          <t>2026/10/10 00:57:17</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:05</t>
+          <t>2026-10-11 00:00:05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4982,144 +5031,188 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/10/12 00:00:05</t>
+          <t>2026/10/11 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-13 00:03:04</t>
+          <t>2026-10-12 00:00:05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>673.13</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/10/13 00:03:04</t>
+          <t>2026/10/12 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 01:52:24</t>
+          <t>2026-10-13 00:03:04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>672.98</t>
+          <t>673.13</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/10/14 01:52:24</t>
+          <t>2026/10/13 00:03:04</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-15 01:02:29</t>
+          <t>2026-10-14 01:52:24</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>672.49</t>
+          <t>672.98</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/10/15 01:02:29</t>
+          <t>2026/10/14 01:52:24</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-16 00:47:35</t>
+          <t>2026-10-15 01:02:29</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>672.53</t>
+          <t>672.49</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/10/16 00:47:35</t>
+          <t>2026/10/15 01:02:29</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-17 02:42:41</t>
+          <t>2026-10-16 00:47:35</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>672.2</t>
+          <t>672.53</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/10/17 02:42:41</t>
+          <t>2026/10/16 00:47:35</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-10-17 02:42:41</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>672.2</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026/10/17 02:42:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>2026-10-18 00:00:05</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>672.2</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>2026/10/18 00:00:05</t>
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-10-19 00:00:05</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>672.2</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026/10/19 00:00:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E21"/>
+  <autoFilter ref="A1:E22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$76</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4344,8 +4344,60 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-10-19 05:30:00</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>667.68</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>667.68</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>670.49</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>670.49</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>672.2</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2026/10/19 05:30:00</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2026-10-18 23:21:07</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J75"/>
+  <autoFilter ref="A1:J76"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4750,7 +4802,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
         <v>672.2</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$77</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4396,8 +4396,60 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-10-19 09:19:09</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>667.58</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>667.58</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>670.39</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>670.39</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>672.08</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2026/10/19 09:19:09</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2026-10-19 01:26:41</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J76"/>
+  <autoFilter ref="A1:J77"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4802,13 +4854,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>672.2</v>
+        <v>672.16</v>
       </c>
       <c r="D22" t="n">
-        <v>672.2</v>
+        <v>672.08</v>
       </c>
       <c r="E22" t="n">
         <v>672.2</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$78</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4448,8 +4448,60 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-10-19 14:37:55</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>666.97</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>666.97</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>669.78</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>669.78</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>672.08</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>2026/10/19 14:37:55</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:39:15</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J77"/>
+  <autoFilter ref="A1:J78"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4854,10 +4906,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>672.16</v>
+        <v>672.14</v>
       </c>
       <c r="D22" t="n">
         <v>672.08</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4500,8 +4500,60 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-10-19 21:52:57</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>666.91</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>666.91</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>669.72</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>669.72</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>672.08</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>2026/10/19 21:52:57</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:57:26</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J78"/>
+  <autoFilter ref="A1:J79"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4906,10 +4958,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>672.14</v>
+        <v>672.128</v>
       </c>
       <c r="D22" t="n">
         <v>672.08</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$79</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4552,8 +4552,60 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-10-20 02:51:46</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>667.07</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>667.07</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>669.88</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>669.88</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>672.08</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2026/10/20 02:51:46</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2026-10-19 19:45:28</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J79"/>
+  <autoFilter ref="A1:J80"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4564,7 +4616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4970,68 +5022,65 @@
         <v>672.2</v>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>672.08</v>
+      </c>
+      <c r="D23" t="n">
+        <v>672.08</v>
+      </c>
+      <c r="E23" t="n">
+        <v>672.08</v>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-01 02:49:02</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>673.51</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/10/01 02:49:02</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:05</t>
+          <t>2026-10-01 02:49:02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -5041,19 +5090,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/10/02 00:00:05</t>
+          <t>2026/10/01 02:49:02</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-03 00:00:05</t>
+          <t>2026-10-02 00:00:05</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5063,19 +5112,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/10/03 00:00:05</t>
+          <t>2026/10/02 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-04 00:00:05</t>
+          <t>2026-10-03 00:00:05</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5085,19 +5134,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/10/04 00:00:05</t>
+          <t>2026/10/03 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-05 00:00:05</t>
+          <t>2026-10-04 00:00:05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5107,19 +5156,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/10/05 00:00:05</t>
+          <t>2026/10/04 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 00:00:05</t>
+          <t>2026-10-05 00:00:05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5129,19 +5178,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/10/06 00:00:05</t>
+          <t>2026/10/05 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-07 00:00:05</t>
+          <t>2026-10-06 00:00:05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5151,19 +5200,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/10/07 00:00:05</t>
+          <t>2026/10/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-08 00:00:05</t>
+          <t>2026-10-07 00:00:05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5173,63 +5222,63 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/10/08 00:00:05</t>
+          <t>2026/10/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-09 01:51:55</t>
+          <t>2026-10-08 00:00:05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>673.67</t>
+          <t>673.51</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/10/09 01:51:55</t>
+          <t>2026/10/08 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-10 00:57:17</t>
+          <t>2026-10-09 01:51:55</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>673.67</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/10/10 00:57:17</t>
+          <t>2026/10/09 01:51:55</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-11 00:00:05</t>
+          <t>2026-10-10 00:57:17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5239,19 +5288,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/10/11 00:00:05</t>
+          <t>2026/10/10 00:57:17</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:05</t>
+          <t>2026-10-11 00:00:05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5261,129 +5310,129 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/10/12 00:00:05</t>
+          <t>2026/10/11 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-13 00:03:04</t>
+          <t>2026-10-12 00:00:05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>673.13</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/10/13 00:03:04</t>
+          <t>2026/10/12 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 01:52:24</t>
+          <t>2026-10-13 00:03:04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>672.98</t>
+          <t>673.13</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/10/14 01:52:24</t>
+          <t>2026/10/13 00:03:04</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-15 01:02:29</t>
+          <t>2026-10-14 01:52:24</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>672.49</t>
+          <t>672.98</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/10/15 01:02:29</t>
+          <t>2026/10/14 01:52:24</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-16 00:47:35</t>
+          <t>2026-10-15 01:02:29</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>672.53</t>
+          <t>672.49</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/10/16 00:47:35</t>
+          <t>2026/10/15 01:02:29</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-17 02:42:41</t>
+          <t>2026-10-16 00:47:35</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>672.2</t>
+          <t>672.53</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/10/17 02:42:41</t>
+          <t>2026/10/16 00:47:35</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:05</t>
+          <t>2026-10-17 02:42:41</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5393,34 +5442,78 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/10/18 00:00:05</t>
+          <t>2026/10/17 02:42:41</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-10-18 00:00:05</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>672.2</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026/10/18 00:00:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>2026-10-19 00:00:05</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>672.2</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>2026/10/19 00:00:05</t>
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-10-20 02:51:46</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>672.08</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026/10/20 02:51:46</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E22"/>
+  <autoFilter ref="A1:E23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$81</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4604,8 +4604,60 @@
         </is>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:40:30</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>667.07</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>667.07</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>669.88</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>669.88</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>672.08</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2026/10/20 06:40:30</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:07:01</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J80"/>
+  <autoFilter ref="A1:J81"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5029,7 +5081,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
         <v>672.08</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$82</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4656,8 +4656,60 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-10-20 09:43:00</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>666.84</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>666.84</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>669.65</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>669.65</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2026/10/20 09:43:00</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2026-10-20 01:47:36</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J81"/>
+  <autoFilter ref="A1:J82"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5081,13 +5133,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>672.08</v>
+        <v>672.0533</v>
       </c>
       <c r="D23" t="n">
-        <v>672.08</v>
+        <v>672</v>
       </c>
       <c r="E23" t="n">
         <v>672.08</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$83</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4708,8 +4708,60 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:38:01</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>666.74</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>666.74</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>669.55</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>669.55</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2026/10/20 14:38:01</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:43:10</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J82"/>
+  <autoFilter ref="A1:J83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5133,10 +5185,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>672.0533</v>
+        <v>672.04</v>
       </c>
       <c r="D23" t="n">
         <v>672</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4760,8 +4760,60 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-10-20 20:13:02</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>666.64</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>666.64</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>669.45</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>669.45</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>2026/10/20 20:13:02</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:16:39</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J83"/>
+  <autoFilter ref="A1:J84"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5185,10 +5237,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>672.04</v>
+        <v>672.032</v>
       </c>
       <c r="D23" t="n">
         <v>672</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4812,8 +4812,60 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-10-21 01:18:04</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>666.65</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>666.65</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>669.46</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>669.46</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2026/10/21 01:18:04</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2026-10-20 17:19:34</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J84"/>
+  <autoFilter ref="A1:J85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4824,7 +4876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5249,68 +5301,65 @@
         <v>672.08</v>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>672</v>
+      </c>
+      <c r="D24" t="n">
+        <v>672</v>
+      </c>
+      <c r="E24" t="n">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-01 02:49:02</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>673.51</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/10/01 02:49:02</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:05</t>
+          <t>2026-10-01 02:49:02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5320,19 +5369,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/10/02 00:00:05</t>
+          <t>2026/10/01 02:49:02</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-03 00:00:05</t>
+          <t>2026-10-02 00:00:05</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5342,19 +5391,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/10/03 00:00:05</t>
+          <t>2026/10/02 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-04 00:00:05</t>
+          <t>2026-10-03 00:00:05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5364,19 +5413,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/10/04 00:00:05</t>
+          <t>2026/10/03 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-05 00:00:05</t>
+          <t>2026-10-04 00:00:05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5386,19 +5435,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/10/05 00:00:05</t>
+          <t>2026/10/04 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 00:00:05</t>
+          <t>2026-10-05 00:00:05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5408,19 +5457,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/10/06 00:00:05</t>
+          <t>2026/10/05 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-07 00:00:05</t>
+          <t>2026-10-06 00:00:05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5430,19 +5479,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/10/07 00:00:05</t>
+          <t>2026/10/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-08 00:00:05</t>
+          <t>2026-10-07 00:00:05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5452,63 +5501,63 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/10/08 00:00:05</t>
+          <t>2026/10/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-09 01:51:55</t>
+          <t>2026-10-08 00:00:05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>673.67</t>
+          <t>673.51</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/10/09 01:51:55</t>
+          <t>2026/10/08 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-10 00:57:17</t>
+          <t>2026-10-09 01:51:55</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>673.67</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/10/10 00:57:17</t>
+          <t>2026/10/09 01:51:55</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-11 00:00:05</t>
+          <t>2026-10-10 00:57:17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5518,19 +5567,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/10/11 00:00:05</t>
+          <t>2026/10/10 00:57:17</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:05</t>
+          <t>2026-10-11 00:00:05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5540,129 +5589,129 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/10/12 00:00:05</t>
+          <t>2026/10/11 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-13 00:03:04</t>
+          <t>2026-10-12 00:00:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>673.13</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/10/13 00:03:04</t>
+          <t>2026/10/12 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 01:52:24</t>
+          <t>2026-10-13 00:03:04</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>672.98</t>
+          <t>673.13</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/10/14 01:52:24</t>
+          <t>2026/10/13 00:03:04</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-15 01:02:29</t>
+          <t>2026-10-14 01:52:24</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>672.49</t>
+          <t>672.98</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/10/15 01:02:29</t>
+          <t>2026/10/14 01:52:24</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-16 00:47:35</t>
+          <t>2026-10-15 01:02:29</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>672.53</t>
+          <t>672.49</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/10/16 00:47:35</t>
+          <t>2026/10/15 01:02:29</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-17 02:42:41</t>
+          <t>2026-10-16 00:47:35</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>672.2</t>
+          <t>672.53</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/10/17 02:42:41</t>
+          <t>2026/10/16 00:47:35</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:05</t>
+          <t>2026-10-17 02:42:41</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5672,19 +5721,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/10/18 00:00:05</t>
+          <t>2026/10/17 02:42:41</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:05</t>
+          <t>2026-10-18 00:00:05</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5694,34 +5743,78 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/10/19 00:00:05</t>
+          <t>2026/10/18 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-10-19 00:00:05</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>672.2</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026/10/19 00:00:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>2026-10-20 02:51:46</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>672.08</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>2026/10/20 02:51:46</t>
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-10-21 01:18:04</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026/10/21 01:18:04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E23"/>
+  <autoFilter ref="A1:E24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$86</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4864,8 +4864,60 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-10-21 02:50:33</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>666.73</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>666.73</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>669.54</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>669.54</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2026/10/21 02:50:33</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2026-10-20 20:43:06</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J85"/>
+  <autoFilter ref="A1:J86"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5308,7 +5360,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
         <v>672</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$87</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4916,8 +4916,60 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:38:02</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>666.73</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>666.73</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>669.54</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>669.54</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2026/10/21 06:38:02</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2026-10-20 23:26:32</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J86"/>
+  <autoFilter ref="A1:J87"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5360,7 +5412,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24" t="n">
         <v>672</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4968,8 +4968,60 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-10-21 09:48:06</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>666.71</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>666.71</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>669.52</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>669.52</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>671.92</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2026/10/21 09:48:06</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2026-10-21 01:53:12</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J87"/>
+  <autoFilter ref="A1:J88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5412,13 +5464,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>672</v>
+        <v>671.98</v>
       </c>
       <c r="D24" t="n">
-        <v>672</v>
+        <v>671.92</v>
       </c>
       <c r="E24" t="n">
         <v>672</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$89</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5020,8 +5020,60 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:53:07</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>666.74</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>666.74</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>669.55</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>669.55</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>671.92</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2026/10/21 14:53:07</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:58:09</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J88"/>
+  <autoFilter ref="A1:J89"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5464,10 +5516,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24" t="n">
-        <v>671.98</v>
+        <v>671.968</v>
       </c>
       <c r="D24" t="n">
         <v>671.92</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$90</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5072,8 +5072,60 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-10-21 20:48:08</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>666.43</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>666.43</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>669.24</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>669.24</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>671.92</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2026/10/21 20:48:08</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:51:32</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J89"/>
+  <autoFilter ref="A1:J90"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5516,10 +5568,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>671.968</v>
+        <v>671.96</v>
       </c>
       <c r="D24" t="n">
         <v>671.92</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$90</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5124,8 +5124,60 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-10-22 01:43:09</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>666.42</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>666.42</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>669.23</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>669.23</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>671.92</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2026/10/22 01:43:09</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2026-10-21 17:47:08</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J90"/>
+  <autoFilter ref="A1:J91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5136,7 +5188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5580,68 +5632,65 @@
         <v>672</v>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>671.92</v>
+      </c>
+      <c r="D25" t="n">
+        <v>671.92</v>
+      </c>
+      <c r="E25" t="n">
+        <v>671.92</v>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-01 02:49:02</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>673.51</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/10/01 02:49:02</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:05</t>
+          <t>2026-10-01 02:49:02</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5651,19 +5700,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/10/02 00:00:05</t>
+          <t>2026/10/01 02:49:02</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-03 00:00:05</t>
+          <t>2026-10-02 00:00:05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5673,19 +5722,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/10/03 00:00:05</t>
+          <t>2026/10/02 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-04 00:00:05</t>
+          <t>2026-10-03 00:00:05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5695,19 +5744,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/10/04 00:00:05</t>
+          <t>2026/10/03 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-05 00:00:05</t>
+          <t>2026-10-04 00:00:05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5717,19 +5766,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/10/05 00:00:05</t>
+          <t>2026/10/04 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 00:00:05</t>
+          <t>2026-10-05 00:00:05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5739,19 +5788,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/10/06 00:00:05</t>
+          <t>2026/10/05 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-07 00:00:05</t>
+          <t>2026-10-06 00:00:05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5761,19 +5810,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/10/07 00:00:05</t>
+          <t>2026/10/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-08 00:00:05</t>
+          <t>2026-10-07 00:00:05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5783,63 +5832,63 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/10/08 00:00:05</t>
+          <t>2026/10/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-09 01:51:55</t>
+          <t>2026-10-08 00:00:05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>673.67</t>
+          <t>673.51</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/10/09 01:51:55</t>
+          <t>2026/10/08 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-10 00:57:17</t>
+          <t>2026-10-09 01:51:55</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>673.67</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/10/10 00:57:17</t>
+          <t>2026/10/09 01:51:55</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-11 00:00:05</t>
+          <t>2026-10-10 00:57:17</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5849,19 +5898,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/10/11 00:00:05</t>
+          <t>2026/10/10 00:57:17</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:05</t>
+          <t>2026-10-11 00:00:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5871,129 +5920,129 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/10/12 00:00:05</t>
+          <t>2026/10/11 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-13 00:03:04</t>
+          <t>2026-10-12 00:00:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>673.13</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/10/13 00:03:04</t>
+          <t>2026/10/12 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 01:52:24</t>
+          <t>2026-10-13 00:03:04</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>672.98</t>
+          <t>673.13</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/10/14 01:52:24</t>
+          <t>2026/10/13 00:03:04</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-15 01:02:29</t>
+          <t>2026-10-14 01:52:24</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>672.49</t>
+          <t>672.98</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/10/15 01:02:29</t>
+          <t>2026/10/14 01:52:24</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-16 00:47:35</t>
+          <t>2026-10-15 01:02:29</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>672.53</t>
+          <t>672.49</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/10/16 00:47:35</t>
+          <t>2026/10/15 01:02:29</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-17 02:42:41</t>
+          <t>2026-10-16 00:47:35</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>672.2</t>
+          <t>672.53</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/10/17 02:42:41</t>
+          <t>2026/10/16 00:47:35</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:05</t>
+          <t>2026-10-17 02:42:41</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6003,19 +6052,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/10/18 00:00:05</t>
+          <t>2026/10/17 02:42:41</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:05</t>
+          <t>2026-10-18 00:00:05</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6025,56 +6074,100 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/10/19 00:00:05</t>
+          <t>2026/10/18 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-20 02:51:46</t>
+          <t>2026-10-19 00:00:05</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>672.08</t>
+          <t>672.2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/10/20 02:51:46</t>
+          <t>2026/10/19 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-10-20 02:51:46</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>672.08</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026/10/20 02:51:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>2026-10-21 01:18:04</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>672</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>2026/10/21 01:18:04</t>
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-10-22 01:43:09</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>671.92</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026/10/22 01:43:09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E24"/>
+  <autoFilter ref="A1:E25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$92</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J91"/>
+  <dimension ref="A1:J92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5176,8 +5176,60 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-10-22 02:50:11</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>666.53</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>666.53</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>669.34</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>669.34</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>671.92</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2026/10/22 02:50:11</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2026-10-21 20:55:29</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J91"/>
+  <autoFilter ref="A1:J92"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5639,7 +5691,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
         <v>671.92</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$93</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J92"/>
+  <dimension ref="A1:J93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5228,8 +5228,60 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-10-22 07:17:32</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>666.53</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>666.53</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>669.34</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>669.34</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>671.92</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2026/10/22 07:17:32</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2026-10-21 23:55:12</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J92"/>
+  <autoFilter ref="A1:J93"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5691,7 +5743,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" t="n">
         <v>671.92</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$94</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J93"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5280,8 +5280,60 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-10-22 11:37:42</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>666.39</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>666.39</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>669.2</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>669.2</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>671.95</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>2026/10/22 11:37:42</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2026-10-22 03:40:04</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J93"/>
+  <autoFilter ref="A1:J94"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5743,16 +5795,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>671.92</v>
+        <v>671.9275</v>
       </c>
       <c r="D25" t="n">
         <v>671.92</v>
       </c>
       <c r="E25" t="n">
-        <v>671.92</v>
+        <v>671.95</v>
       </c>
     </row>
     <row r="26"/>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$95</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J94"/>
+  <dimension ref="A1:J95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5332,8 +5332,60 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:53:13</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>666.23</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>666.23</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>669.04</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>669.04</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>671.95</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2026/10/22 16:53:13</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2026-10-22 08:55:29</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J94"/>
+  <autoFilter ref="A1:J95"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5795,10 +5847,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" t="n">
-        <v>671.9275</v>
+        <v>671.932</v>
       </c>
       <c r="D25" t="n">
         <v>671.92</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$96</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J95"/>
+  <dimension ref="A1:J96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5384,8 +5384,60 @@
         </is>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-10-22 22:18:14</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>666.44</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>666.44</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>669.25</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>669.25</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>671.95</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2026/10/22 22:18:14</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:23:51</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J95"/>
+  <autoFilter ref="A1:J96"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5847,10 +5899,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>671.932</v>
+        <v>671.9349999999999</v>
       </c>
       <c r="D25" t="n">
         <v>671.92</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$96</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J96"/>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5436,8 +5436,60 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-10-23 02:38:15</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>666.41</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>666.41</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>669.22</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>669.22</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>671.95</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2026/10/23 02:38:15</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2026-10-22 18:41:17</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J96"/>
+  <autoFilter ref="A1:J97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5448,7 +5500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5911,68 +5963,65 @@
         <v>671.95</v>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>671.95</v>
+      </c>
+      <c r="D26" t="n">
+        <v>671.95</v>
+      </c>
+      <c r="E26" t="n">
+        <v>671.95</v>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-01 02:49:02</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>673.51</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/10/01 02:49:02</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:05</t>
+          <t>2026-10-01 02:49:02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5982,19 +6031,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/10/02 00:00:05</t>
+          <t>2026/10/01 02:49:02</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-03 00:00:05</t>
+          <t>2026-10-02 00:00:05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -6004,19 +6053,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/10/03 00:00:05</t>
+          <t>2026/10/02 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-04 00:00:05</t>
+          <t>2026-10-03 00:00:05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -6026,19 +6075,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/10/04 00:00:05</t>
+          <t>2026/10/03 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-05 00:00:05</t>
+          <t>2026-10-04 00:00:05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -6048,19 +6097,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/10/05 00:00:05</t>
+          <t>2026/10/04 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 00:00:05</t>
+          <t>2026-10-05 00:00:05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -6070,19 +6119,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/10/06 00:00:05</t>
+          <t>2026/10/05 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-07 00:00:05</t>
+          <t>2026-10-06 00:00:05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -6092,19 +6141,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/10/07 00:00:05</t>
+          <t>2026/10/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-08 00:00:05</t>
+          <t>2026-10-07 00:00:05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -6114,63 +6163,63 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/10/08 00:00:05</t>
+          <t>2026/10/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-09 01:51:55</t>
+          <t>2026-10-08 00:00:05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>673.67</t>
+          <t>673.51</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/10/09 01:51:55</t>
+          <t>2026/10/08 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-10 00:57:17</t>
+          <t>2026-10-09 01:51:55</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>673.67</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/10/10 00:57:17</t>
+          <t>2026/10/09 01:51:55</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-11 00:00:05</t>
+          <t>2026-10-10 00:57:17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -6180,19 +6229,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/10/11 00:00:05</t>
+          <t>2026/10/10 00:57:17</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:05</t>
+          <t>2026-10-11 00:00:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -6202,129 +6251,129 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/10/12 00:00:05</t>
+          <t>2026/10/11 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-13 00:03:04</t>
+          <t>2026-10-12 00:00:05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>673.13</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/10/13 00:03:04</t>
+          <t>2026/10/12 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 01:52:24</t>
+          <t>2026-10-13 00:03:04</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>672.98</t>
+          <t>673.13</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/10/14 01:52:24</t>
+          <t>2026/10/13 00:03:04</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-15 01:02:29</t>
+          <t>2026-10-14 01:52:24</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>672.49</t>
+          <t>672.98</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/10/15 01:02:29</t>
+          <t>2026/10/14 01:52:24</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-16 00:47:35</t>
+          <t>2026-10-15 01:02:29</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>672.53</t>
+          <t>672.49</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/10/16 00:47:35</t>
+          <t>2026/10/15 01:02:29</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-17 02:42:41</t>
+          <t>2026-10-16 00:47:35</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>672.2</t>
+          <t>672.53</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/10/17 02:42:41</t>
+          <t>2026/10/16 00:47:35</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:05</t>
+          <t>2026-10-17 02:42:41</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6334,19 +6383,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/10/18 00:00:05</t>
+          <t>2026/10/17 02:42:41</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:05</t>
+          <t>2026-10-18 00:00:05</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6356,78 +6405,122 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/10/19 00:00:05</t>
+          <t>2026/10/18 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-20 02:51:46</t>
+          <t>2026-10-19 00:00:05</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>672.08</t>
+          <t>672.2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/10/20 02:51:46</t>
+          <t>2026/10/19 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-21 01:18:04</t>
+          <t>2026-10-20 02:51:46</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>672.08</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/10/21 01:18:04</t>
+          <t>2026/10/20 02:51:46</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-10-21 01:18:04</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026/10/21 01:18:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>2026-10-22 01:43:09</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>671.92</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>2026/10/22 01:43:09</t>
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-10-23 02:38:15</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>671.95</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026/10/23 02:38:15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E25"/>
+  <autoFilter ref="A1:E26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$98</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J97"/>
+  <dimension ref="A1:J98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5488,8 +5488,60 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-10-23 05:30:00</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>666.51</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>666.51</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>669.32</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>669.32</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>671.95</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2026/10/23 05:30:00</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2026-10-22 21:55:43</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J97"/>
+  <autoFilter ref="A1:J98"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5970,7 +6022,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
         <v>671.95</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$99</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J98"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5540,8 +5540,60 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-10-23 07:55:07</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>666.51</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>666.51</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>669.32</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>669.32</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>671.95</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>2026/10/23 07:55:07</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2026-10-23 00:26:49</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J98"/>
+  <autoFilter ref="A1:J99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6022,7 +6074,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C26" t="n">
         <v>671.95</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$100</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J99"/>
+  <dimension ref="A1:J100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5592,8 +5592,60 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-10-23 13:09:46</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>666.25</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>666.25</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>669.06</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>669.06</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>671.8</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2026/10/23 13:09:46</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2026-10-23 05:13:26</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J99"/>
+  <autoFilter ref="A1:J100"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6074,13 +6126,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>671.95</v>
+        <v>671.9125</v>
       </c>
       <c r="D26" t="n">
-        <v>671.95</v>
+        <v>671.8</v>
       </c>
       <c r="E26" t="n">
         <v>671.95</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$101</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J100"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5644,8 +5644,60 @@
         </is>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-10-23 18:03:19</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>665.96</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>665.96</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>668.76</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>668.76</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>671.8</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>2026/10/23 18:03:19</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:09:34</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J100"/>
+  <autoFilter ref="A1:J101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6126,10 +6178,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>671.9125</v>
+        <v>671.89</v>
       </c>
       <c r="D26" t="n">
         <v>671.8</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$102</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5696,8 +5696,60 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2026-10-23 22:58:20</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>665.96</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>665.96</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>668.76</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>668.76</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>671.8</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>2026/10/23 22:58:20</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2026-10-23 15:03:52</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J101"/>
+  <autoFilter ref="A1:J102"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6178,10 +6230,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>671.89</v>
+        <v>671.875</v>
       </c>
       <c r="D26" t="n">
         <v>671.8</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$102</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J102"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5748,8 +5748,60 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026-10-24 02:53:52</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>666.06</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>666.06</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>668.86</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>668.86</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>671.8</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>2026/10/24 02:53:52</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2026-10-23 19:07:29</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J102"/>
+  <autoFilter ref="A1:J103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5760,7 +5812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6242,68 +6294,65 @@
         <v>671.95</v>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>671.8</v>
+      </c>
+      <c r="D27" t="n">
+        <v>671.8</v>
+      </c>
+      <c r="E27" t="n">
+        <v>671.8</v>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-01 02:49:02</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>673.51</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/10/01 02:49:02</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:05</t>
+          <t>2026-10-01 02:49:02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -6313,19 +6362,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/10/02 00:00:05</t>
+          <t>2026/10/01 02:49:02</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-03 00:00:05</t>
+          <t>2026-10-02 00:00:05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -6335,19 +6384,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/10/03 00:00:05</t>
+          <t>2026/10/02 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-04 00:00:05</t>
+          <t>2026-10-03 00:00:05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -6357,19 +6406,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/10/04 00:00:05</t>
+          <t>2026/10/03 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-05 00:00:05</t>
+          <t>2026-10-04 00:00:05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -6379,19 +6428,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/10/05 00:00:05</t>
+          <t>2026/10/04 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 00:00:05</t>
+          <t>2026-10-05 00:00:05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -6401,19 +6450,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/10/06 00:00:05</t>
+          <t>2026/10/05 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-07 00:00:05</t>
+          <t>2026-10-06 00:00:05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -6423,19 +6472,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/10/07 00:00:05</t>
+          <t>2026/10/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-08 00:00:05</t>
+          <t>2026-10-07 00:00:05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -6445,63 +6494,63 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/10/08 00:00:05</t>
+          <t>2026/10/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-09 01:51:55</t>
+          <t>2026-10-08 00:00:05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>673.67</t>
+          <t>673.51</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/10/09 01:51:55</t>
+          <t>2026/10/08 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-10 00:57:17</t>
+          <t>2026-10-09 01:51:55</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>673.67</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/10/10 00:57:17</t>
+          <t>2026/10/09 01:51:55</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-11 00:00:05</t>
+          <t>2026-10-10 00:57:17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -6511,19 +6560,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/10/11 00:00:05</t>
+          <t>2026/10/10 00:57:17</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:05</t>
+          <t>2026-10-11 00:00:05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6533,129 +6582,129 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/10/12 00:00:05</t>
+          <t>2026/10/11 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-13 00:03:04</t>
+          <t>2026-10-12 00:00:05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>673.13</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/10/13 00:03:04</t>
+          <t>2026/10/12 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 01:52:24</t>
+          <t>2026-10-13 00:03:04</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>672.98</t>
+          <t>673.13</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/10/14 01:52:24</t>
+          <t>2026/10/13 00:03:04</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-15 01:02:29</t>
+          <t>2026-10-14 01:52:24</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>672.49</t>
+          <t>672.98</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/10/15 01:02:29</t>
+          <t>2026/10/14 01:52:24</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-16 00:47:35</t>
+          <t>2026-10-15 01:02:29</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>672.53</t>
+          <t>672.49</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/10/16 00:47:35</t>
+          <t>2026/10/15 01:02:29</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-17 02:42:41</t>
+          <t>2026-10-16 00:47:35</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>672.2</t>
+          <t>672.53</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/10/17 02:42:41</t>
+          <t>2026/10/16 00:47:35</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:05</t>
+          <t>2026-10-17 02:42:41</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6665,19 +6714,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/10/18 00:00:05</t>
+          <t>2026/10/17 02:42:41</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:05</t>
+          <t>2026-10-18 00:00:05</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6687,100 +6736,144 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/10/19 00:00:05</t>
+          <t>2026/10/18 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-20 02:51:46</t>
+          <t>2026-10-19 00:00:05</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>672.08</t>
+          <t>672.2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/10/20 02:51:46</t>
+          <t>2026/10/19 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-21 01:18:04</t>
+          <t>2026-10-20 02:51:46</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>672.08</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/10/21 01:18:04</t>
+          <t>2026/10/20 02:51:46</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-22 01:43:09</t>
+          <t>2026-10-21 01:18:04</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>671.92</t>
+          <t>672</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/10/22 01:43:09</t>
+          <t>2026/10/21 01:18:04</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-10-22 01:43:09</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>671.92</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026/10/22 01:43:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>2026-10-23 02:38:15</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>671.95</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>2026/10/23 02:38:15</t>
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-10-24 02:53:52</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>671.8</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026/10/24 02:53:52</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E26"/>
+  <autoFilter ref="A1:E27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$104</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:J104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5800,8 +5800,60 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2026-10-24 05:30:00</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>666.06</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>666.06</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>668.86</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>668.86</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>671.8</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2026/10/24 05:30:00</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2026-10-23 22:06:50</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J103"/>
+  <autoFilter ref="A1:J104"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6301,7 +6353,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
         <v>671.8</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$105</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J104"/>
+  <dimension ref="A1:J105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5852,8 +5852,60 @@
         </is>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2026-10-24 10:30:00</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>666.06</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>666.06</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>668.86</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>668.86</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>671.8</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2026/10/24 10:30:00</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2026-10-24 05:01:47</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J104"/>
+  <autoFilter ref="A1:J105"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6353,7 +6405,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" t="n">
         <v>671.8</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$105</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J105"/>
+  <dimension ref="A1:J106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5904,8 +5904,60 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026-10-25 00:00:05</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>666.06</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>666.06</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>668.86</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>668.86</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>671.8</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2026/10/25 00:00:05</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>2026-10-24 16:53:25</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J105"/>
+  <autoFilter ref="A1:J106"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5916,7 +5968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6417,68 +6469,65 @@
         <v>671.8</v>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>671.8</v>
+      </c>
+      <c r="D28" t="n">
+        <v>671.8</v>
+      </c>
+      <c r="E28" t="n">
+        <v>671.8</v>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-01 02:49:02</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>673.51</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/10/01 02:49:02</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:05</t>
+          <t>2026-10-01 02:49:02</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -6488,19 +6537,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/10/02 00:00:05</t>
+          <t>2026/10/01 02:49:02</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-03 00:00:05</t>
+          <t>2026-10-02 00:00:05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -6510,19 +6559,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/10/03 00:00:05</t>
+          <t>2026/10/02 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-04 00:00:05</t>
+          <t>2026-10-03 00:00:05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -6532,19 +6581,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/10/04 00:00:05</t>
+          <t>2026/10/03 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-05 00:00:05</t>
+          <t>2026-10-04 00:00:05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -6554,19 +6603,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/10/05 00:00:05</t>
+          <t>2026/10/04 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 00:00:05</t>
+          <t>2026-10-05 00:00:05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -6576,19 +6625,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/10/06 00:00:05</t>
+          <t>2026/10/05 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-07 00:00:05</t>
+          <t>2026-10-06 00:00:05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -6598,19 +6647,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/10/07 00:00:05</t>
+          <t>2026/10/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-08 00:00:05</t>
+          <t>2026-10-07 00:00:05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -6620,63 +6669,63 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/10/08 00:00:05</t>
+          <t>2026/10/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-09 01:51:55</t>
+          <t>2026-10-08 00:00:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>673.67</t>
+          <t>673.51</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/10/09 01:51:55</t>
+          <t>2026/10/08 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-10 00:57:17</t>
+          <t>2026-10-09 01:51:55</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>673.67</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/10/10 00:57:17</t>
+          <t>2026/10/09 01:51:55</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-11 00:00:05</t>
+          <t>2026-10-10 00:57:17</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6686,19 +6735,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/10/11 00:00:05</t>
+          <t>2026/10/10 00:57:17</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:05</t>
+          <t>2026-10-11 00:00:05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6708,129 +6757,129 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/10/12 00:00:05</t>
+          <t>2026/10/11 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-13 00:03:04</t>
+          <t>2026-10-12 00:00:05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>673.13</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/10/13 00:03:04</t>
+          <t>2026/10/12 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 01:52:24</t>
+          <t>2026-10-13 00:03:04</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>672.98</t>
+          <t>673.13</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/10/14 01:52:24</t>
+          <t>2026/10/13 00:03:04</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-15 01:02:29</t>
+          <t>2026-10-14 01:52:24</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>672.49</t>
+          <t>672.98</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/10/15 01:02:29</t>
+          <t>2026/10/14 01:52:24</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-16 00:47:35</t>
+          <t>2026-10-15 01:02:29</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>672.53</t>
+          <t>672.49</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/10/16 00:47:35</t>
+          <t>2026/10/15 01:02:29</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-17 02:42:41</t>
+          <t>2026-10-16 00:47:35</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>672.2</t>
+          <t>672.53</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/10/17 02:42:41</t>
+          <t>2026/10/16 00:47:35</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:05</t>
+          <t>2026-10-17 02:42:41</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6840,19 +6889,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/10/18 00:00:05</t>
+          <t>2026/10/17 02:42:41</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:05</t>
+          <t>2026-10-18 00:00:05</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6862,122 +6911,166 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/10/19 00:00:05</t>
+          <t>2026/10/18 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-20 02:51:46</t>
+          <t>2026-10-19 00:00:05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>672.08</t>
+          <t>672.2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/10/20 02:51:46</t>
+          <t>2026/10/19 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-21 01:18:04</t>
+          <t>2026-10-20 02:51:46</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>672.08</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/10/21 01:18:04</t>
+          <t>2026/10/20 02:51:46</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-22 01:43:09</t>
+          <t>2026-10-21 01:18:04</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>671.92</t>
+          <t>672</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026/10/22 01:43:09</t>
+          <t>2026/10/21 01:18:04</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-23 02:38:15</t>
+          <t>2026-10-22 01:43:09</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>671.95</t>
+          <t>671.92</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/10/23 02:38:15</t>
+          <t>2026/10/22 01:43:09</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-10-23 02:38:15</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>671.95</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026/10/23 02:38:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>2026-10-24 02:53:52</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>671.8</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>2026/10/24 02:53:52</t>
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-10-25 00:00:05</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>671.8</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026/10/25 00:00:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E27"/>
+  <autoFilter ref="A1:E28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$107</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J106"/>
+  <dimension ref="A1:J107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5956,8 +5956,60 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2026-10-25 05:30:00</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>666.06</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>666.06</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>668.86</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>668.86</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>671.8</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2026/10/25 05:30:00</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>2026-10-24 21:38:23</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J106"/>
+  <autoFilter ref="A1:J107"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6476,7 +6528,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
         <v>671.8</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$108</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J107"/>
+  <dimension ref="A1:J108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6008,8 +6008,60 @@
         </is>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026-10-25 10:30:00</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>666.06</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>666.06</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>668.86</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>668.86</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>671.8</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2026/10/25 10:30:00</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>2026-10-25 06:56:26</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J107"/>
+  <autoFilter ref="A1:J108"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6528,7 +6580,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C28" t="n">
         <v>671.8</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$108</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J108"/>
+  <dimension ref="A1:J109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6060,8 +6060,60 @@
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2026-10-26 00:00:05</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>666.06</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>666.06</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>668.86</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>668.86</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>671.8</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>2026/10/26 00:00:05</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>2026-10-25 16:41:07</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J108"/>
+  <autoFilter ref="A1:J109"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6072,7 +6124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6592,68 +6644,65 @@
         <v>671.8</v>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>671.8</v>
+      </c>
+      <c r="D29" t="n">
+        <v>671.8</v>
+      </c>
+      <c r="E29" t="n">
+        <v>671.8</v>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-01 02:49:02</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>673.51</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/10/01 02:49:02</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:05</t>
+          <t>2026-10-01 02:49:02</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -6663,19 +6712,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/10/02 00:00:05</t>
+          <t>2026/10/01 02:49:02</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-03 00:00:05</t>
+          <t>2026-10-02 00:00:05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -6685,19 +6734,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/10/03 00:00:05</t>
+          <t>2026/10/02 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-04 00:00:05</t>
+          <t>2026-10-03 00:00:05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -6707,19 +6756,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/10/04 00:00:05</t>
+          <t>2026/10/03 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-05 00:00:05</t>
+          <t>2026-10-04 00:00:05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -6729,19 +6778,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/10/05 00:00:05</t>
+          <t>2026/10/04 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 00:00:05</t>
+          <t>2026-10-05 00:00:05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -6751,19 +6800,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/10/06 00:00:05</t>
+          <t>2026/10/05 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-07 00:00:05</t>
+          <t>2026-10-06 00:00:05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -6773,19 +6822,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/10/07 00:00:05</t>
+          <t>2026/10/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-08 00:00:05</t>
+          <t>2026-10-07 00:00:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -6795,63 +6844,63 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/10/08 00:00:05</t>
+          <t>2026/10/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-09 01:51:55</t>
+          <t>2026-10-08 00:00:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>673.67</t>
+          <t>673.51</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/10/09 01:51:55</t>
+          <t>2026/10/08 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-10 00:57:17</t>
+          <t>2026-10-09 01:51:55</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>673.67</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/10/10 00:57:17</t>
+          <t>2026/10/09 01:51:55</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-11 00:00:05</t>
+          <t>2026-10-10 00:57:17</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6861,19 +6910,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/10/11 00:00:05</t>
+          <t>2026/10/10 00:57:17</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:05</t>
+          <t>2026-10-11 00:00:05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6883,129 +6932,129 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/10/12 00:00:05</t>
+          <t>2026/10/11 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-13 00:03:04</t>
+          <t>2026-10-12 00:00:05</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>673.13</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/10/13 00:03:04</t>
+          <t>2026/10/12 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 01:52:24</t>
+          <t>2026-10-13 00:03:04</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>672.98</t>
+          <t>673.13</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/10/14 01:52:24</t>
+          <t>2026/10/13 00:03:04</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-15 01:02:29</t>
+          <t>2026-10-14 01:52:24</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>672.49</t>
+          <t>672.98</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/10/15 01:02:29</t>
+          <t>2026/10/14 01:52:24</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-16 00:47:35</t>
+          <t>2026-10-15 01:02:29</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>672.53</t>
+          <t>672.49</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/10/16 00:47:35</t>
+          <t>2026/10/15 01:02:29</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-17 02:42:41</t>
+          <t>2026-10-16 00:47:35</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>672.2</t>
+          <t>672.53</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/10/17 02:42:41</t>
+          <t>2026/10/16 00:47:35</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:05</t>
+          <t>2026-10-17 02:42:41</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7015,19 +7064,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/10/18 00:00:05</t>
+          <t>2026/10/17 02:42:41</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:05</t>
+          <t>2026-10-18 00:00:05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7037,144 +7086,188 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/10/19 00:00:05</t>
+          <t>2026/10/18 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-20 02:51:46</t>
+          <t>2026-10-19 00:00:05</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>672.08</t>
+          <t>672.2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/10/20 02:51:46</t>
+          <t>2026/10/19 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-21 01:18:04</t>
+          <t>2026-10-20 02:51:46</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>672.08</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026/10/21 01:18:04</t>
+          <t>2026/10/20 02:51:46</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-22 01:43:09</t>
+          <t>2026-10-21 01:18:04</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>671.92</t>
+          <t>672</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/10/22 01:43:09</t>
+          <t>2026/10/21 01:18:04</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-23 02:38:15</t>
+          <t>2026-10-22 01:43:09</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>671.95</t>
+          <t>671.92</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026/10/23 02:38:15</t>
+          <t>2026/10/22 01:43:09</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-24 02:53:52</t>
+          <t>2026-10-23 02:38:15</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>671.8</t>
+          <t>671.95</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026/10/24 02:53:52</t>
+          <t>2026/10/23 02:38:15</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-10-24 02:53:52</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>671.8</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026/10/24 02:53:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>2026-10-25 00:00:05</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>671.8</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>2026/10/25 00:00:05</t>
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-10-26 00:00:05</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>671.8</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026/10/26 00:00:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E28"/>
+  <autoFilter ref="A1:E29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$110</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J109"/>
+  <dimension ref="A1:J110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6112,8 +6112,60 @@
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2026-10-26 05:30:00</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>666.06</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>666.06</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>668.86</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>668.86</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>671.8</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2026/10/26 05:30:00</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:53:43</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J109"/>
+  <autoFilter ref="A1:J110"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6651,7 +6703,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
         <v>671.8</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$111</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J110"/>
+  <dimension ref="A1:J111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6164,8 +6164,60 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2026-10-26 07:36:13</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>666.06</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>666.06</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>668.86</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>668.86</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>671.8</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>2026/10/26 07:36:13</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>2026-10-25 23:47:10</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J110"/>
+  <autoFilter ref="A1:J111"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6703,7 +6755,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
         <v>671.8</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$112</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J111"/>
+  <dimension ref="A1:J112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6216,8 +6216,60 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:47:59</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>665.8</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>665.8</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>668.6</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>668.6</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>671.62</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2026/10/26 09:47:59</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>2026-10-26 01:49:25</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J111"/>
+  <autoFilter ref="A1:J112"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6755,13 +6807,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>671.8</v>
+        <v>671.755</v>
       </c>
       <c r="D29" t="n">
-        <v>671.8</v>
+        <v>671.62</v>
       </c>
       <c r="E29" t="n">
         <v>671.8</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$113</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J112"/>
+  <dimension ref="A1:J113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6268,8 +6268,60 @@
         </is>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2026-10-26 15:03:33</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>665.63</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>665.63</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>668.43</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>668.43</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>671.62</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2026/10/26 15:03:33</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>2026-10-26 07:06:54</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J112"/>
+  <autoFilter ref="A1:J113"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6807,10 +6859,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>671.755</v>
+        <v>671.728</v>
       </c>
       <c r="D29" t="n">
         <v>671.62</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$114</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J113"/>
+  <dimension ref="A1:J114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6320,8 +6320,60 @@
         </is>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026-10-26 22:08:34</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>665.74</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>665.74</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>668.54</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>668.54</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>671.62</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>2026/10/26 22:08:34</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>2026-10-26 14:13:02</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J113"/>
+  <autoFilter ref="A1:J114"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6859,10 +6911,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>671.728</v>
+        <v>671.71</v>
       </c>
       <c r="D29" t="n">
         <v>671.62</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$114</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J114"/>
+  <dimension ref="A1:J115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6372,8 +6372,60 @@
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026-10-27 02:49:24</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>665.93</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>665.93</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>668.73</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>668.73</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>671.62</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2026/10/27 02:49:24</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>2026-10-26 19:58:08</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J114"/>
+  <autoFilter ref="A1:J115"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6384,7 +6436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6923,68 +6975,65 @@
         <v>671.8</v>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>671.62</v>
+      </c>
+      <c r="D30" t="n">
+        <v>671.62</v>
+      </c>
+      <c r="E30" t="n">
+        <v>671.62</v>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-01 02:49:02</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>673.51</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/10/01 02:49:02</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:05</t>
+          <t>2026-10-01 02:49:02</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -6994,19 +7043,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/10/02 00:00:05</t>
+          <t>2026/10/01 02:49:02</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-03 00:00:05</t>
+          <t>2026-10-02 00:00:05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -7016,19 +7065,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/10/03 00:00:05</t>
+          <t>2026/10/02 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-04 00:00:05</t>
+          <t>2026-10-03 00:00:05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -7038,19 +7087,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/10/04 00:00:05</t>
+          <t>2026/10/03 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-05 00:00:05</t>
+          <t>2026-10-04 00:00:05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -7060,19 +7109,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/10/05 00:00:05</t>
+          <t>2026/10/04 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 00:00:05</t>
+          <t>2026-10-05 00:00:05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -7082,19 +7131,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/10/06 00:00:05</t>
+          <t>2026/10/05 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-07 00:00:05</t>
+          <t>2026-10-06 00:00:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -7104,19 +7153,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/10/07 00:00:05</t>
+          <t>2026/10/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-08 00:00:05</t>
+          <t>2026-10-07 00:00:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -7126,63 +7175,63 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/10/08 00:00:05</t>
+          <t>2026/10/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-09 01:51:55</t>
+          <t>2026-10-08 00:00:05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>673.67</t>
+          <t>673.51</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/10/09 01:51:55</t>
+          <t>2026/10/08 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-10 00:57:17</t>
+          <t>2026-10-09 01:51:55</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>673.67</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/10/10 00:57:17</t>
+          <t>2026/10/09 01:51:55</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-11 00:00:05</t>
+          <t>2026-10-10 00:57:17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -7192,19 +7241,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/10/11 00:00:05</t>
+          <t>2026/10/10 00:57:17</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:05</t>
+          <t>2026-10-11 00:00:05</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -7214,129 +7263,129 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/10/12 00:00:05</t>
+          <t>2026/10/11 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-13 00:03:04</t>
+          <t>2026-10-12 00:00:05</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>673.13</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/10/13 00:03:04</t>
+          <t>2026/10/12 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 01:52:24</t>
+          <t>2026-10-13 00:03:04</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>672.98</t>
+          <t>673.13</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/10/14 01:52:24</t>
+          <t>2026/10/13 00:03:04</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-15 01:02:29</t>
+          <t>2026-10-14 01:52:24</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>672.49</t>
+          <t>672.98</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/10/15 01:02:29</t>
+          <t>2026/10/14 01:52:24</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-16 00:47:35</t>
+          <t>2026-10-15 01:02:29</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>672.53</t>
+          <t>672.49</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/10/16 00:47:35</t>
+          <t>2026/10/15 01:02:29</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-17 02:42:41</t>
+          <t>2026-10-16 00:47:35</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>672.2</t>
+          <t>672.53</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/10/17 02:42:41</t>
+          <t>2026/10/16 00:47:35</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:05</t>
+          <t>2026-10-17 02:42:41</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7346,19 +7395,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/10/18 00:00:05</t>
+          <t>2026/10/17 02:42:41</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:05</t>
+          <t>2026-10-18 00:00:05</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7368,129 +7417,129 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/10/19 00:00:05</t>
+          <t>2026/10/18 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-20 02:51:46</t>
+          <t>2026-10-19 00:00:05</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>672.08</t>
+          <t>672.2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026/10/20 02:51:46</t>
+          <t>2026/10/19 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-21 01:18:04</t>
+          <t>2026-10-20 02:51:46</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>672.08</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/10/21 01:18:04</t>
+          <t>2026/10/20 02:51:46</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-22 01:43:09</t>
+          <t>2026-10-21 01:18:04</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>671.92</t>
+          <t>672</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026/10/22 01:43:09</t>
+          <t>2026/10/21 01:18:04</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-23 02:38:15</t>
+          <t>2026-10-22 01:43:09</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>671.95</t>
+          <t>671.92</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026/10/23 02:38:15</t>
+          <t>2026/10/22 01:43:09</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-24 02:53:52</t>
+          <t>2026-10-23 02:38:15</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>671.8</t>
+          <t>671.95</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026/10/24 02:53:52</t>
+          <t>2026/10/23 02:38:15</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-25 00:00:05</t>
+          <t>2026-10-24 02:53:52</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -7500,34 +7549,78 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026/10/25 00:00:05</t>
+          <t>2026/10/24 02:53:52</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-10-25 00:00:05</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>671.8</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026/10/25 00:00:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>2026-10-26 00:00:05</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>671.8</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>2026/10/26 00:00:05</t>
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-10-27 02:49:24</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>671.62</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026/10/27 02:49:24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E29"/>
+  <autoFilter ref="A1:E30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$116</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J115"/>
+  <dimension ref="A1:J116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6424,8 +6424,60 @@
         </is>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026-10-27 06:51:08</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>665.93</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>665.93</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>668.73</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>668.73</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>671.62</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2026/10/27 06:51:08</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2026-10-26 23:43:52</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J115"/>
+  <autoFilter ref="A1:J116"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6982,7 +7034,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
         <v>671.62</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$117</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J116"/>
+  <dimension ref="A1:J117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6476,8 +6476,60 @@
         </is>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:23:37</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>665.67</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>665.67</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>668.47</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>668.47</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>671.71</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>2026/10/27 10:23:37</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2026-10-27 02:27:02</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J116"/>
+  <autoFilter ref="A1:J117"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7034,16 +7086,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C30" t="n">
-        <v>671.62</v>
+        <v>671.65</v>
       </c>
       <c r="D30" t="n">
         <v>671.62</v>
       </c>
       <c r="E30" t="n">
-        <v>671.62</v>
+        <v>671.71</v>
       </c>
     </row>
     <row r="31"/>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$118</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J117"/>
+  <dimension ref="A1:J118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6528,8 +6528,60 @@
         </is>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2026-10-27 16:13:39</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>665.66</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>665.66</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>668.46</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>668.46</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>671.71</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2026/10/27 16:13:39</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>2026-10-27 08:17:22</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J117"/>
+  <autoFilter ref="A1:J118"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7086,10 +7138,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>671.65</v>
+        <v>671.665</v>
       </c>
       <c r="D30" t="n">
         <v>671.62</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$119</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J118"/>
+  <dimension ref="A1:J119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6580,8 +6580,60 @@
         </is>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:34:30</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>665.59</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>665.59</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>668.39</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>668.39</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>671.71</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2026/10/27 22:34:30</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:39:55</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J118"/>
+  <autoFilter ref="A1:J119"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7138,10 +7190,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>671.665</v>
+        <v>671.674</v>
       </c>
       <c r="D30" t="n">
         <v>671.62</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$119</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J119"/>
+  <dimension ref="A1:J120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6632,8 +6632,60 @@
         </is>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026-10-28 02:51:04</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>665.58</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>665.58</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>668.38</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>668.38</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>671.71</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2026/10/28 02:51:04</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>2026-10-27 19:39:26</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J119"/>
+  <autoFilter ref="A1:J120"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6644,7 +6696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7202,68 +7254,65 @@
         <v>671.71</v>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>671.71</v>
+      </c>
+      <c r="D31" t="n">
+        <v>671.71</v>
+      </c>
+      <c r="E31" t="n">
+        <v>671.71</v>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-01 02:49:02</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>673.51</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/10/01 02:49:02</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:05</t>
+          <t>2026-10-01 02:49:02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -7273,19 +7322,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/10/02 00:00:05</t>
+          <t>2026/10/01 02:49:02</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-03 00:00:05</t>
+          <t>2026-10-02 00:00:05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -7295,19 +7344,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/10/03 00:00:05</t>
+          <t>2026/10/02 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-04 00:00:05</t>
+          <t>2026-10-03 00:00:05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -7317,19 +7366,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/10/04 00:00:05</t>
+          <t>2026/10/03 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-05 00:00:05</t>
+          <t>2026-10-04 00:00:05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -7339,19 +7388,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/10/05 00:00:05</t>
+          <t>2026/10/04 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 00:00:05</t>
+          <t>2026-10-05 00:00:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -7361,19 +7410,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/10/06 00:00:05</t>
+          <t>2026/10/05 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-07 00:00:05</t>
+          <t>2026-10-06 00:00:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -7383,19 +7432,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/10/07 00:00:05</t>
+          <t>2026/10/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-08 00:00:05</t>
+          <t>2026-10-07 00:00:05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -7405,63 +7454,63 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/10/08 00:00:05</t>
+          <t>2026/10/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-09 01:51:55</t>
+          <t>2026-10-08 00:00:05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>673.67</t>
+          <t>673.51</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/10/09 01:51:55</t>
+          <t>2026/10/08 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-10 00:57:17</t>
+          <t>2026-10-09 01:51:55</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>673.67</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/10/10 00:57:17</t>
+          <t>2026/10/09 01:51:55</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-11 00:00:05</t>
+          <t>2026-10-10 00:57:17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -7471,19 +7520,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/10/11 00:00:05</t>
+          <t>2026/10/10 00:57:17</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:05</t>
+          <t>2026-10-11 00:00:05</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -7493,129 +7542,129 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/10/12 00:00:05</t>
+          <t>2026/10/11 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-13 00:03:04</t>
+          <t>2026-10-12 00:00:05</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>673.13</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/10/13 00:03:04</t>
+          <t>2026/10/12 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 01:52:24</t>
+          <t>2026-10-13 00:03:04</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>672.98</t>
+          <t>673.13</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/10/14 01:52:24</t>
+          <t>2026/10/13 00:03:04</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-15 01:02:29</t>
+          <t>2026-10-14 01:52:24</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>672.49</t>
+          <t>672.98</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/10/15 01:02:29</t>
+          <t>2026/10/14 01:52:24</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-16 00:47:35</t>
+          <t>2026-10-15 01:02:29</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>672.53</t>
+          <t>672.49</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/10/16 00:47:35</t>
+          <t>2026/10/15 01:02:29</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-17 02:42:41</t>
+          <t>2026-10-16 00:47:35</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>672.2</t>
+          <t>672.53</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/10/17 02:42:41</t>
+          <t>2026/10/16 00:47:35</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:05</t>
+          <t>2026-10-17 02:42:41</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7625,19 +7674,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/10/18 00:00:05</t>
+          <t>2026/10/17 02:42:41</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:05</t>
+          <t>2026-10-18 00:00:05</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7647,129 +7696,129 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026/10/19 00:00:05</t>
+          <t>2026/10/18 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-20 02:51:46</t>
+          <t>2026-10-19 00:00:05</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>672.08</t>
+          <t>672.2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/10/20 02:51:46</t>
+          <t>2026/10/19 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-21 01:18:04</t>
+          <t>2026-10-20 02:51:46</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>672.08</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026/10/21 01:18:04</t>
+          <t>2026/10/20 02:51:46</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-22 01:43:09</t>
+          <t>2026-10-21 01:18:04</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>671.92</t>
+          <t>672</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026/10/22 01:43:09</t>
+          <t>2026/10/21 01:18:04</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-23 02:38:15</t>
+          <t>2026-10-22 01:43:09</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>671.95</t>
+          <t>671.92</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026/10/23 02:38:15</t>
+          <t>2026/10/22 01:43:09</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-24 02:53:52</t>
+          <t>2026-10-23 02:38:15</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>671.8</t>
+          <t>671.95</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026/10/24 02:53:52</t>
+          <t>2026/10/23 02:38:15</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-10-25 00:00:05</t>
+          <t>2026-10-24 02:53:52</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -7779,19 +7828,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026/10/25 00:00:05</t>
+          <t>2026/10/24 02:53:52</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-10-26 00:00:05</t>
+          <t>2026-10-25 00:00:05</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -7801,34 +7850,78 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026/10/26 00:00:05</t>
+          <t>2026/10/25 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-10-26 00:00:05</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>671.8</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026/10/26 00:00:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>2026-10-27 02:49:24</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>671.62</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>2026/10/27 02:49:24</t>
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-10-28 02:51:04</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>671.71</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026/10/28 02:51:04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E30"/>
+  <autoFilter ref="A1:E31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$121</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J120"/>
+  <dimension ref="A1:J121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6684,8 +6684,60 @@
         </is>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2026-10-28 06:41:13</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>665.58</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>665.58</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>668.38</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>668.38</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>671.71</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2026/10/28 06:41:13</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:13:01</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J120"/>
+  <autoFilter ref="A1:J121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7261,7 +7313,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
         <v>671.71</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$122</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J121"/>
+  <dimension ref="A1:J122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6736,8 +6736,60 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2026-10-28 10:18:43</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>665.61</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>665.61</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>668.41</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>668.41</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>671.65</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>2026/10/28 10:18:43</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>2026-10-28 02:20:33</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J121"/>
+  <autoFilter ref="A1:J122"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7313,13 +7365,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>671.71</v>
+        <v>671.6900000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>671.71</v>
+        <v>671.65</v>
       </c>
       <c r="E31" t="n">
         <v>671.71</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$123</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J122"/>
+  <dimension ref="A1:J123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6788,8 +6788,60 @@
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2026-10-28 16:43:44</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>665.49</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>665.49</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>668.29</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>668.29</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>671.65</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>2026/10/28 16:43:44</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>2026-10-28 08:45:15</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J122"/>
+  <autoFilter ref="A1:J123"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7365,10 +7417,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>671.6900000000001</v>
+        <v>671.6799999999999</v>
       </c>
       <c r="D31" t="n">
         <v>671.65</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$124</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J123"/>
+  <dimension ref="A1:J124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6840,8 +6840,60 @@
         </is>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2026-10-28 23:23:46</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>665.44</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>665.44</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>668.24</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>668.24</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>671.65</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>2026/10/28 23:23:46</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>2026-10-28 15:30:01</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J123"/>
+  <autoFilter ref="A1:J124"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7417,10 +7469,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>671.6799999999999</v>
+        <v>671.674</v>
       </c>
       <c r="D31" t="n">
         <v>671.65</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$124</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J124"/>
+  <dimension ref="A1:J125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6892,8 +6892,60 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2026-10-29 02:50:19</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>665.49</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>665.49</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>668.29</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>668.29</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>671.65</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>2026/10/29 02:50:19</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>2026-10-28 20:30:59</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J124"/>
+  <autoFilter ref="A1:J125"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6904,7 +6956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7481,68 +7533,65 @@
         <v>671.71</v>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="n">
+        <v>671.65</v>
+      </c>
+      <c r="D32" t="n">
+        <v>671.65</v>
+      </c>
+      <c r="E32" t="n">
+        <v>671.65</v>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-01 02:49:02</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>673.51</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/10/01 02:49:02</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:05</t>
+          <t>2026-10-01 02:49:02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -7552,19 +7601,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/10/02 00:00:05</t>
+          <t>2026/10/01 02:49:02</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-03 00:00:05</t>
+          <t>2026-10-02 00:00:05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -7574,19 +7623,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/10/03 00:00:05</t>
+          <t>2026/10/02 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-04 00:00:05</t>
+          <t>2026-10-03 00:00:05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -7596,19 +7645,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/10/04 00:00:05</t>
+          <t>2026/10/03 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-05 00:00:05</t>
+          <t>2026-10-04 00:00:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -7618,19 +7667,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/10/05 00:00:05</t>
+          <t>2026/10/04 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 00:00:05</t>
+          <t>2026-10-05 00:00:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -7640,19 +7689,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/10/06 00:00:05</t>
+          <t>2026/10/05 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-07 00:00:05</t>
+          <t>2026-10-06 00:00:05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -7662,19 +7711,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/10/07 00:00:05</t>
+          <t>2026/10/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-08 00:00:05</t>
+          <t>2026-10-07 00:00:05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -7684,63 +7733,63 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/10/08 00:00:05</t>
+          <t>2026/10/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-09 01:51:55</t>
+          <t>2026-10-08 00:00:05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>673.67</t>
+          <t>673.51</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/10/09 01:51:55</t>
+          <t>2026/10/08 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-10 00:57:17</t>
+          <t>2026-10-09 01:51:55</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>673.67</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/10/10 00:57:17</t>
+          <t>2026/10/09 01:51:55</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-11 00:00:05</t>
+          <t>2026-10-10 00:57:17</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -7750,19 +7799,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/10/11 00:00:05</t>
+          <t>2026/10/10 00:57:17</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:05</t>
+          <t>2026-10-11 00:00:05</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -7772,129 +7821,129 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/10/12 00:00:05</t>
+          <t>2026/10/11 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-13 00:03:04</t>
+          <t>2026-10-12 00:00:05</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>673.13</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/10/13 00:03:04</t>
+          <t>2026/10/12 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 01:52:24</t>
+          <t>2026-10-13 00:03:04</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>672.98</t>
+          <t>673.13</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/10/14 01:52:24</t>
+          <t>2026/10/13 00:03:04</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-15 01:02:29</t>
+          <t>2026-10-14 01:52:24</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>672.49</t>
+          <t>672.98</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/10/15 01:02:29</t>
+          <t>2026/10/14 01:52:24</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-16 00:47:35</t>
+          <t>2026-10-15 01:02:29</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>672.53</t>
+          <t>672.49</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/10/16 00:47:35</t>
+          <t>2026/10/15 01:02:29</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-17 02:42:41</t>
+          <t>2026-10-16 00:47:35</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>672.2</t>
+          <t>672.53</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/10/17 02:42:41</t>
+          <t>2026/10/16 00:47:35</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:05</t>
+          <t>2026-10-17 02:42:41</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7904,19 +7953,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026/10/18 00:00:05</t>
+          <t>2026/10/17 02:42:41</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:05</t>
+          <t>2026-10-18 00:00:05</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7926,129 +7975,129 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/10/19 00:00:05</t>
+          <t>2026/10/18 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-20 02:51:46</t>
+          <t>2026-10-19 00:00:05</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>672.08</t>
+          <t>672.2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026/10/20 02:51:46</t>
+          <t>2026/10/19 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-21 01:18:04</t>
+          <t>2026-10-20 02:51:46</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>672.08</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026/10/21 01:18:04</t>
+          <t>2026/10/20 02:51:46</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-22 01:43:09</t>
+          <t>2026-10-21 01:18:04</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>671.92</t>
+          <t>672</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026/10/22 01:43:09</t>
+          <t>2026/10/21 01:18:04</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-23 02:38:15</t>
+          <t>2026-10-22 01:43:09</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>671.95</t>
+          <t>671.92</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026/10/23 02:38:15</t>
+          <t>2026/10/22 01:43:09</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-10-24 02:53:52</t>
+          <t>2026-10-23 02:38:15</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>671.8</t>
+          <t>671.95</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026/10/24 02:53:52</t>
+          <t>2026/10/23 02:38:15</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-10-25 00:00:05</t>
+          <t>2026-10-24 02:53:52</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8058,19 +8107,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026/10/25 00:00:05</t>
+          <t>2026/10/24 02:53:52</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-26 00:00:05</t>
+          <t>2026-10-25 00:00:05</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8080,56 +8129,100 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026/10/26 00:00:05</t>
+          <t>2026/10/25 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-10-27 02:49:24</t>
+          <t>2026-10-26 00:00:05</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>671.62</t>
+          <t>671.8</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026/10/27 02:49:24</t>
+          <t>2026/10/26 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-10-27 02:49:24</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>671.62</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026/10/27 02:49:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>2026-10-28 02:51:04</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>671.71</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>2026/10/28 02:51:04</t>
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-10-29 02:50:19</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>671.65</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026/10/29 02:50:19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E31"/>
+  <autoFilter ref="A1:E32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$126</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J125"/>
+  <dimension ref="A1:J126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6944,8 +6944,60 @@
         </is>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2026-10-29 07:55:29</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>665.49</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>665.49</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>668.29</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>668.29</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>671.65</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>2026/10/29 07:55:29</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>2026-10-29 00:19:54</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J125"/>
+  <autoFilter ref="A1:J126"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7540,7 +7592,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" t="n">
         <v>671.65</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$127</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J126"/>
+  <dimension ref="A1:J127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6996,8 +6996,60 @@
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2026-10-29 13:58:49</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>665.08</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>665.08</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>667.88</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>667.88</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>671.47</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>2026/10/29 13:58:49</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>2026-10-29 06:03:06</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J126"/>
+  <autoFilter ref="A1:J127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7592,13 +7644,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>671.65</v>
+        <v>671.59</v>
       </c>
       <c r="D32" t="n">
-        <v>671.65</v>
+        <v>671.47</v>
       </c>
       <c r="E32" t="n">
         <v>671.65</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$128</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J127"/>
+  <dimension ref="A1:J128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7048,8 +7048,60 @@
         </is>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:48:51</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>665.06</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>665.06</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>667.86</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>667.86</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>671.47</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>2026/10/29 20:48:51</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>2026-10-29 12:51:54</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J127"/>
+  <autoFilter ref="A1:J128"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7644,10 +7696,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>671.59</v>
+        <v>671.5599999999999</v>
       </c>
       <c r="D32" t="n">
         <v>671.47</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$128</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7100,8 +7100,60 @@
         </is>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2026-10-30 02:43:52</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>665.04</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>665.04</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>667.84</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>667.84</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>671.47</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>2026/10/30 02:43:52</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>2026-10-29 18:44:33</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J128"/>
+  <autoFilter ref="A1:J129"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7112,7 +7164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7708,68 +7760,65 @@
         <v>671.65</v>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="n">
+        <v>671.47</v>
+      </c>
+      <c r="D33" t="n">
+        <v>671.47</v>
+      </c>
+      <c r="E33" t="n">
+        <v>671.47</v>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-01 02:49:02</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>673.51</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/10/01 02:49:02</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:05</t>
+          <t>2026-10-01 02:49:02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -7779,19 +7828,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/10/02 00:00:05</t>
+          <t>2026/10/01 02:49:02</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-03 00:00:05</t>
+          <t>2026-10-02 00:00:05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -7801,19 +7850,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/10/03 00:00:05</t>
+          <t>2026/10/02 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-04 00:00:05</t>
+          <t>2026-10-03 00:00:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -7823,19 +7872,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/10/04 00:00:05</t>
+          <t>2026/10/03 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-05 00:00:05</t>
+          <t>2026-10-04 00:00:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -7845,19 +7894,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/10/05 00:00:05</t>
+          <t>2026/10/04 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 00:00:05</t>
+          <t>2026-10-05 00:00:05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -7867,19 +7916,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/10/06 00:00:05</t>
+          <t>2026/10/05 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-07 00:00:05</t>
+          <t>2026-10-06 00:00:05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -7889,19 +7938,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/10/07 00:00:05</t>
+          <t>2026/10/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-08 00:00:05</t>
+          <t>2026-10-07 00:00:05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -7911,63 +7960,63 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/10/08 00:00:05</t>
+          <t>2026/10/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-09 01:51:55</t>
+          <t>2026-10-08 00:00:05</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>673.67</t>
+          <t>673.51</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/10/09 01:51:55</t>
+          <t>2026/10/08 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-10 00:57:17</t>
+          <t>2026-10-09 01:51:55</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>673.67</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/10/10 00:57:17</t>
+          <t>2026/10/09 01:51:55</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-11 00:00:05</t>
+          <t>2026-10-10 00:57:17</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -7977,19 +8026,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/10/11 00:00:05</t>
+          <t>2026/10/10 00:57:17</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:05</t>
+          <t>2026-10-11 00:00:05</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -7999,129 +8048,129 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/10/12 00:00:05</t>
+          <t>2026/10/11 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-13 00:03:04</t>
+          <t>2026-10-12 00:00:05</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>673.13</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/10/13 00:03:04</t>
+          <t>2026/10/12 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 01:52:24</t>
+          <t>2026-10-13 00:03:04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>672.98</t>
+          <t>673.13</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/10/14 01:52:24</t>
+          <t>2026/10/13 00:03:04</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-15 01:02:29</t>
+          <t>2026-10-14 01:52:24</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>672.49</t>
+          <t>672.98</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/10/15 01:02:29</t>
+          <t>2026/10/14 01:52:24</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-16 00:47:35</t>
+          <t>2026-10-15 01:02:29</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>672.53</t>
+          <t>672.49</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/10/16 00:47:35</t>
+          <t>2026/10/15 01:02:29</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-17 02:42:41</t>
+          <t>2026-10-16 00:47:35</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>672.2</t>
+          <t>672.53</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026/10/17 02:42:41</t>
+          <t>2026/10/16 00:47:35</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:05</t>
+          <t>2026-10-17 02:42:41</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -8131,19 +8180,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/10/18 00:00:05</t>
+          <t>2026/10/17 02:42:41</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:05</t>
+          <t>2026-10-18 00:00:05</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -8153,129 +8202,129 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026/10/19 00:00:05</t>
+          <t>2026/10/18 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-20 02:51:46</t>
+          <t>2026-10-19 00:00:05</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>672.08</t>
+          <t>672.2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026/10/20 02:51:46</t>
+          <t>2026/10/19 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-21 01:18:04</t>
+          <t>2026-10-20 02:51:46</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>672.08</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026/10/21 01:18:04</t>
+          <t>2026/10/20 02:51:46</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-22 01:43:09</t>
+          <t>2026-10-21 01:18:04</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>671.92</t>
+          <t>672</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026/10/22 01:43:09</t>
+          <t>2026/10/21 01:18:04</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-10-23 02:38:15</t>
+          <t>2026-10-22 01:43:09</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>671.95</t>
+          <t>671.92</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026/10/23 02:38:15</t>
+          <t>2026/10/22 01:43:09</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-10-24 02:53:52</t>
+          <t>2026-10-23 02:38:15</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>671.8</t>
+          <t>671.95</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026/10/24 02:53:52</t>
+          <t>2026/10/23 02:38:15</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-25 00:00:05</t>
+          <t>2026-10-24 02:53:52</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8285,19 +8334,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026/10/25 00:00:05</t>
+          <t>2026/10/24 02:53:52</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-10-26 00:00:05</t>
+          <t>2026-10-25 00:00:05</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8307,78 +8356,122 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026/10/26 00:00:05</t>
+          <t>2026/10/25 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-10-27 02:49:24</t>
+          <t>2026-10-26 00:00:05</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>671.62</t>
+          <t>671.8</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026/10/27 02:49:24</t>
+          <t>2026/10/26 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-10-28 02:51:04</t>
+          <t>2026-10-27 02:49:24</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>671.71</t>
+          <t>671.62</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026/10/28 02:51:04</t>
+          <t>2026/10/27 02:49:24</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-10-28 02:51:04</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>671.71</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026/10/28 02:51:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>2026-10-29 02:50:19</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>671.65</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>2026/10/29 02:50:19</t>
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-10-30 02:43:52</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>671.47</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026/10/30 02:43:52</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E32"/>
+  <autoFilter ref="A1:E33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$130</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J129"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7152,8 +7152,60 @@
         </is>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2026-10-30 06:42:22</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>665.13</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>665.13</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>667.93</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>667.93</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>671.47</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>2026/10/30 06:42:22</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>2026-10-29 23:00:11</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J129"/>
+  <autoFilter ref="A1:J130"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7767,7 +7819,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33" t="n">
         <v>671.47</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$131</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J130"/>
+  <dimension ref="A1:J131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7204,8 +7204,60 @@
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2026-10-30 10:30:00</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>664.84</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>664.84</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>667.64</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>667.64</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>671.38</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>2026/10/30 10:30:00</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>2026-10-30 02:31:46</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J130"/>
+  <autoFilter ref="A1:J131"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7819,13 +7871,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C33" t="n">
-        <v>671.47</v>
+        <v>671.4400000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>671.47</v>
+        <v>671.38</v>
       </c>
       <c r="E33" t="n">
         <v>671.47</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$132</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J131"/>
+  <dimension ref="A1:J132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7256,8 +7256,60 @@
         </is>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2026-10-30 16:53:56</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>664.26</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>664.26</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>667.05</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>667.05</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>671.38</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>2026/10/30 16:53:56</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>2026-10-30 08:56:17</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J131"/>
+  <autoFilter ref="A1:J132"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7871,10 +7923,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>671.4400000000001</v>
+        <v>671.425</v>
       </c>
       <c r="D33" t="n">
         <v>671.38</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$133</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J132"/>
+  <dimension ref="A1:J133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7308,8 +7308,60 @@
         </is>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2026-10-30 23:38:57</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>664.33</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>664.33</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>667.12</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>667.12</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>671.38</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>2026/10/30 23:38:57</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>2026-10-30 15:43:17</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J132"/>
+  <autoFilter ref="A1:J133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7923,10 +7975,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>671.425</v>
+        <v>671.4160000000001</v>
       </c>
       <c r="D33" t="n">
         <v>671.38</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$133</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J133"/>
+  <dimension ref="A1:J134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7360,8 +7360,60 @@
         </is>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2026-10-31 02:50:16</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>664.49</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>664.49</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>667.28</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>667.28</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>671.38</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>2026/10/31 02:50:16</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>2026-10-30 20:09:13</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J133"/>
+  <autoFilter ref="A1:J134"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7372,7 +7424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7987,68 +8039,65 @@
         <v>671.47</v>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="n">
+        <v>671.38</v>
+      </c>
+      <c r="D34" t="n">
+        <v>671.38</v>
+      </c>
+      <c r="E34" t="n">
+        <v>671.38</v>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Day First Published (Middle)</t>
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>firstPublishTime</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>middle</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>publishTimeRaw</t>
-        </is>
-      </c>
-    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-01 02:49:02</t>
+          <t>firstPublishTime</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>673.51</t>
+          <t>middle</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/10/01 02:49:02</t>
+          <t>publishTimeRaw</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 00:00:05</t>
+          <t>2026-10-01 02:49:02</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -8058,19 +8107,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/10/02 00:00:05</t>
+          <t>2026/10/01 02:49:02</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-03 00:00:05</t>
+          <t>2026-10-02 00:00:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -8080,19 +8129,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/10/03 00:00:05</t>
+          <t>2026/10/02 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-04 00:00:05</t>
+          <t>2026-10-03 00:00:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -8102,19 +8151,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/10/04 00:00:05</t>
+          <t>2026/10/03 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-05 00:00:05</t>
+          <t>2026-10-04 00:00:05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -8124,19 +8173,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/10/05 00:00:05</t>
+          <t>2026/10/04 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 00:00:05</t>
+          <t>2026-10-05 00:00:05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -8146,19 +8195,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/10/06 00:00:05</t>
+          <t>2026/10/05 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-07 00:00:05</t>
+          <t>2026-10-06 00:00:05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -8168,19 +8217,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/10/07 00:00:05</t>
+          <t>2026/10/06 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-08 00:00:05</t>
+          <t>2026-10-07 00:00:05</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -8190,63 +8239,63 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/10/08 00:00:05</t>
+          <t>2026/10/07 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-09 01:51:55</t>
+          <t>2026-10-08 00:00:05</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>673.67</t>
+          <t>673.51</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/10/09 01:51:55</t>
+          <t>2026/10/08 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-10 00:57:17</t>
+          <t>2026-10-09 01:51:55</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>673.3</t>
+          <t>673.67</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/10/10 00:57:17</t>
+          <t>2026/10/09 01:51:55</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-11 00:00:05</t>
+          <t>2026-10-10 00:57:17</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -8256,19 +8305,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/10/11 00:00:05</t>
+          <t>2026/10/10 00:57:17</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:05</t>
+          <t>2026-10-11 00:00:05</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -8278,129 +8327,129 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/10/12 00:00:05</t>
+          <t>2026/10/11 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-13 00:03:04</t>
+          <t>2026-10-12 00:00:05</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>673.13</t>
+          <t>673.3</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/10/13 00:03:04</t>
+          <t>2026/10/12 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 01:52:24</t>
+          <t>2026-10-13 00:03:04</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>672.98</t>
+          <t>673.13</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/10/14 01:52:24</t>
+          <t>2026/10/13 00:03:04</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-15 01:02:29</t>
+          <t>2026-10-14 01:52:24</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>672.49</t>
+          <t>672.98</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/10/15 01:02:29</t>
+          <t>2026/10/14 01:52:24</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-16 00:47:35</t>
+          <t>2026-10-15 01:02:29</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>672.53</t>
+          <t>672.49</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026/10/16 00:47:35</t>
+          <t>2026/10/15 01:02:29</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-17 02:42:41</t>
+          <t>2026-10-16 00:47:35</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>672.2</t>
+          <t>672.53</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/10/17 02:42:41</t>
+          <t>2026/10/16 00:47:35</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-18 00:00:05</t>
+          <t>2026-10-17 02:42:41</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -8410,19 +8459,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026/10/18 00:00:05</t>
+          <t>2026/10/17 02:42:41</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-19 00:00:05</t>
+          <t>2026-10-18 00:00:05</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -8432,129 +8481,129 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026/10/19 00:00:05</t>
+          <t>2026/10/18 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-20 02:51:46</t>
+          <t>2026-10-19 00:00:05</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>672.08</t>
+          <t>672.2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026/10/20 02:51:46</t>
+          <t>2026/10/19 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-21 01:18:04</t>
+          <t>2026-10-20 02:51:46</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>672.08</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026/10/21 01:18:04</t>
+          <t>2026/10/20 02:51:46</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-10-22 01:43:09</t>
+          <t>2026-10-21 01:18:04</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>671.92</t>
+          <t>672</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026/10/22 01:43:09</t>
+          <t>2026/10/21 01:18:04</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-10-23 02:38:15</t>
+          <t>2026-10-22 01:43:09</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>671.95</t>
+          <t>671.92</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026/10/23 02:38:15</t>
+          <t>2026/10/22 01:43:09</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-24 02:53:52</t>
+          <t>2026-10-23 02:38:15</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>671.8</t>
+          <t>671.95</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026/10/24 02:53:52</t>
+          <t>2026/10/23 02:38:15</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-10-25 00:00:05</t>
+          <t>2026-10-24 02:53:52</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8564,19 +8613,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026/10/25 00:00:05</t>
+          <t>2026/10/24 02:53:52</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-10-26 00:00:05</t>
+          <t>2026-10-25 00:00:05</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8586,100 +8635,144 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026/10/26 00:00:05</t>
+          <t>2026/10/25 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-10-27 02:49:24</t>
+          <t>2026-10-26 00:00:05</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>671.62</t>
+          <t>671.8</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026/10/27 02:49:24</t>
+          <t>2026/10/26 00:00:05</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-10-28 02:51:04</t>
+          <t>2026-10-27 02:49:24</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>671.71</t>
+          <t>671.62</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026/10/28 02:51:04</t>
+          <t>2026/10/27 02:49:24</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-10-29 02:50:19</t>
+          <t>2026-10-28 02:51:04</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>671.65</t>
+          <t>671.71</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026/10/29 02:50:19</t>
+          <t>2026/10/28 02:51:04</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-10-29 02:50:19</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>671.65</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026/10/29 02:50:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>2026-10-30 02:43:52</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>671.47</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>2026/10/30 02:43:52</t>
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-10-31 02:50:16</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>671.38</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026/10/31 02:50:16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E33"/>
+  <autoFilter ref="A1:E34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$135</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J134"/>
+  <dimension ref="A1:J135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7412,8 +7412,60 @@
         </is>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2026-10-31 05:30:00</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>664.49</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>664.49</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>667.28</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>667.28</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>671.38</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>2026/10/31 05:30:00</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>2026-10-30 23:45:25</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J134"/>
+  <autoFilter ref="A1:J135"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8046,7 +8098,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34" t="n">
         <v>671.38</v>

--- a/data/2026/2026-10.xlsx
+++ b/data/2026/2026-10.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Published Values'!$A$1:$J$136</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Summary'!$A$1:$E$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J135"/>
+  <dimension ref="A1:J136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7464,8 +7464,60 @@
         </is>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2026-10-31 10:30:00</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>664.49</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>664.49</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>667.28</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>667.28</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>671.38</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>2026/10/31 10:30:00</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>2026-10-31 02:46:31</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>https://www.bankofchina.com/sourcedb/whpj/enindex_1619.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J135"/>
+  <autoFilter ref="A1:J136"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8098,7 +8150,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C34" t="n">
         <v>671.38</v>
